--- a/src/PE1VM1/App/MET/IpcApplication/Vom/Alert/matrix/scc/alert_S_SCB-CSTD-1-02-A-C0.xlsx
+++ b/src/PE1VM1/App/MET/IpcApplication/Vom/Alert/matrix/scc/alert_S_SCB-CSTD-1-02-A-C0.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\work\BEV\イベント\シス検#2\S_ADMID\削除対応\dn-cdc-mcu-AA_BEVS3_CDC_MCU_020_削除対応\src\PE1VM1\App\MET\IpcApplication\Vom\Alert\matrix\scc\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\Z10035B22030582\dn-cdc-mcu-AA_BEVS3_CDC_MCU_020_削除対応\src\PE1VM1\App\MET\IpcApplication\Vom\Alert\matrix\scc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E5E9E52-BB3F-47C1-BA44-122558FD5F95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A2F9E7C-E3BC-436A-A2A1-E98DFBDAA706}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14130" yWindow="-16320" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="1" r:id="rId1"/>
@@ -526,7 +526,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2663" uniqueCount="291">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2470" uniqueCount="272">
   <si>
     <t>更新履歴</t>
     <phoneticPr fontId="2"/>
@@ -2538,41 +2538,10 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>制御仕様→TT</t>
-    <rPh sb="0" eb="5">
-      <t>セイギョシヨウミギ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>制御仕様→BZR</t>
     <rPh sb="0" eb="5">
       <t>セイギョシヨウミギ</t>
     </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>制御仕様→MID</t>
-    <rPh sb="0" eb="5">
-      <t>セイギョシヨウミギ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>IG-ON + 通常 + 非表示 +非吹鳴</t>
-    <rPh sb="8" eb="10">
-      <t>ツウジョウ</t>
-    </rPh>
-    <rPh sb="13" eb="16">
-      <t>ヒヒョウジ</t>
-    </rPh>
-    <rPh sb="18" eb="21">
-      <t>ヒスイメイ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>ABG1S01</t>
     <phoneticPr fontId="2"/>
   </si>
   <si>
@@ -2619,57 +2588,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>01b</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>10b</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>11b</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>非表示(00b)/
-SCB作動(01b)/
-非表示(10b)/
-非表示(11b)/</t>
-    <rPh sb="0" eb="3">
-      <t>ヒヒョウジ</t>
-    </rPh>
-    <rPh sb="13" eb="15">
-      <t>サドウ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>IG-ON + 通常 + 非表示 + 断続</t>
-    <rPh sb="8" eb="10">
-      <t>ツウジョウ</t>
-    </rPh>
-    <rPh sb="13" eb="16">
-      <t>ヒヒョウジ</t>
-    </rPh>
-    <rPh sb="19" eb="21">
-      <t>ダンゾク</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>IG-ON + 通常 + SCB作動 +非吹鳴</t>
-    <rPh sb="8" eb="10">
-      <t>ツウジョウ</t>
-    </rPh>
-    <rPh sb="16" eb="18">
-      <t>サドウ</t>
-    </rPh>
-    <rPh sb="20" eb="23">
-      <t>ヒスイメイ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>ABG1S01_STS</t>
     <phoneticPr fontId="2"/>
   </si>
@@ -2687,27 +2605,6 @@
   </si>
   <si>
     <t>IG-OFF + ** + ** + **</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>IG-ON + 通常 + 非表示 +　断続</t>
-    <rPh sb="8" eb="10">
-      <t>ツウジョウ</t>
-    </rPh>
-    <rPh sb="13" eb="16">
-      <t>ヒヒョウジ</t>
-    </rPh>
-    <rPh sb="19" eb="21">
-      <t>ダンゾク</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>-</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>-</t>
     <phoneticPr fontId="2"/>
   </si>
   <si>
@@ -2741,24 +2638,7 @@
     <t>ALERT_CH_S_SCB</t>
   </si>
   <si>
-    <t>IG-ON + 通常 + SCB作動 + 断続</t>
-    <rPh sb="8" eb="10">
-      <t>ツウジョウ</t>
-    </rPh>
-    <rPh sb="16" eb="18">
-      <t>サドウ</t>
-    </rPh>
-    <rPh sb="21" eb="23">
-      <t>ダンゾク</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>CYCL</t>
-  </si>
-  <si>
-    <t>CYCL</t>
-    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>CYCL</t>
@@ -2775,37 +2655,6 @@
   </si>
   <si>
     <t>断続</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>断続</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>断続</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>UNKNOWN/
-CYCL/
-SCB_OPE/
-CYCL_ON</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>SCB_OPE</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>CYCL_SCB_OPE</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>SCB_OPE</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>SCB_OPE</t>
     <phoneticPr fontId="2"/>
   </si>
   <si>
@@ -2853,27 +2702,11 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>SCSACCEL_SIG</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>SCSBZR_SIG</t>
     <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>S_SCB-CSTD-1-BZR01-REQ02</t>
-  </si>
-  <si>
-    <t>REQ03</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>MET-S_SCB-CSTD-1-02-A-C0.xlsm</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>https://aip01.dndev.net/svn/met/toyota/std/rd/spec/個車/面企画/branches/00.Product/20210219_暫定リリース/MET</t>
-    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>-</t>
@@ -2883,43 +2716,6 @@
     <t>大藤</t>
     <rPh sb="0" eb="2">
       <t>オオフジ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <r>
-      <t>S_SCB-CSTD-1-MEF01-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>REQ03</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="2"/>
-        <charset val="128"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">/
--
-</t>
-    </r>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>制御仕様→VMID</t>
-    <rPh sb="0" eb="5">
-      <t>セイギョシヨウミギ</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
@@ -2997,6 +2793,103 @@
   </si>
   <si>
     <t>ABG1S01_STS</t>
+  </si>
+  <si>
+    <t>1.1.0</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>5.5.0</t>
+  </si>
+  <si>
+    <t>KSE八木春樹</t>
+    <rPh sb="3" eb="7">
+      <t>ヤギハルキ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>BEV シス検#2(流用元：alert_S_SCB-CSTD-1-02-A-C0.c)
+[CH_Design]シート
+PD判定削除に伴い、REQ・機能判定等削除
+[S_SCB]シート
+PD判定削除に伴い、真理値表の修正
+[Reference]シート
+CH削除に伴い、真理値表の修正</t>
+    <rPh sb="6" eb="7">
+      <t>ケン</t>
+    </rPh>
+    <rPh sb="61" eb="65">
+      <t>ハンテイサクジョ</t>
+    </rPh>
+    <rPh sb="66" eb="67">
+      <t>トモナ</t>
+    </rPh>
+    <rPh sb="73" eb="78">
+      <t>キノウハンテイトウ</t>
+    </rPh>
+    <rPh sb="78" eb="80">
+      <t>サクジョ</t>
+    </rPh>
+    <rPh sb="94" eb="96">
+      <t>ハンテイ</t>
+    </rPh>
+    <rPh sb="96" eb="98">
+      <t>サクジョ</t>
+    </rPh>
+    <rPh sb="99" eb="100">
+      <t>トモナ</t>
+    </rPh>
+    <rPh sb="102" eb="106">
+      <t>シンリチヒョウ</t>
+    </rPh>
+    <rPh sb="107" eb="109">
+      <t>シュウセイ</t>
+    </rPh>
+    <rPh sb="118" eb="122">
+      <t>シンリチヒョウ</t>
+    </rPh>
+    <rPh sb="122" eb="124">
+      <t>ツイカ</t>
+    </rPh>
+    <rPh sb="127" eb="129">
+      <t>サクジョ</t>
+    </rPh>
+    <rPh sb="130" eb="131">
+      <t>トモナ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>MET-S_ADBZR-CSTD-0-02-A-C0</t>
+  </si>
+  <si>
+    <t>https://svn.geniie.net/bevs3/bevs3cdc/仕様書/MET/#1/tags/00.Product/v0.2.1</t>
+  </si>
+  <si>
+    <t>UNKNOWN/
+CYCL</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>IG-ON + 通常 + 非吹鳴</t>
+    <rPh sb="8" eb="10">
+      <t>ツウジョウ</t>
+    </rPh>
+    <rPh sb="13" eb="16">
+      <t>ヒスイメイ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>IG-ON + 通常 + 断続</t>
+    <rPh sb="8" eb="10">
+      <t>ツウジョウダンゾク</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t/>
+    </rPh>
+    <phoneticPr fontId="2"/>
   </si>
 </sst>
 </file>
@@ -4354,7 +4247,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="284">
+  <cellXfs count="283">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -4943,9 +4836,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyProtection="1">
       <alignment vertical="center"/>
     </xf>
@@ -4972,9 +4862,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="25" borderId="2" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="24" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="24" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -5003,15 +4890,6 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="16" fillId="7" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -5023,12 +4901,6 @@
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="24" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -5063,16 +4935,37 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="19" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="19" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="19" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="19" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="68" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="50" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="68" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="50" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="69" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="54" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="61" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="19" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -5108,15 +5001,6 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="68" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="50" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="12" borderId="68" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -5126,22 +5010,10 @@
     <xf numFmtId="0" fontId="3" fillId="12" borderId="50" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="68" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="50" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="69" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="54" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="61" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
@@ -5193,6 +5065,24 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="75" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="2" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="2" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="78" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -6083,145 +5973,13 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>20</xdr:col>
-      <xdr:colOff>57051</xdr:colOff>
-      <xdr:row>82</xdr:row>
-      <xdr:rowOff>44824</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>24</xdr:col>
-      <xdr:colOff>664218</xdr:colOff>
-      <xdr:row>98</xdr:row>
-      <xdr:rowOff>156152</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="12" name="図 11">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-00000C000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="16682506" y="16652960"/>
-          <a:ext cx="3378076" cy="2882237"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>20</xdr:col>
-      <xdr:colOff>67235</xdr:colOff>
-      <xdr:row>102</xdr:row>
-      <xdr:rowOff>145675</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>43</xdr:col>
-      <xdr:colOff>661147</xdr:colOff>
-      <xdr:row>113</xdr:row>
-      <xdr:rowOff>33617</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="7" name="図 6">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000007000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="16640735" y="19419793"/>
-          <a:ext cx="16315765" cy="1736913"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>24</xdr:col>
-      <xdr:colOff>667989</xdr:colOff>
-      <xdr:row>82</xdr:row>
-      <xdr:rowOff>136072</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>50</xdr:col>
-      <xdr:colOff>373782</xdr:colOff>
-      <xdr:row>99</xdr:row>
-      <xdr:rowOff>101108</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="6" name="図 5">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000006000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="20064353" y="16744208"/>
-          <a:ext cx="17716702" cy="2909127"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>20</xdr:col>
+      <xdr:col>19</xdr:col>
       <xdr:colOff>231322</xdr:colOff>
       <xdr:row>60</xdr:row>
       <xdr:rowOff>136071</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>46</xdr:col>
+      <xdr:col>45</xdr:col>
       <xdr:colOff>13608</xdr:colOff>
       <xdr:row>69</xdr:row>
       <xdr:rowOff>122464</xdr:rowOff>
@@ -6240,7 +5998,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -6259,13 +6017,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>20</xdr:col>
+      <xdr:col>19</xdr:col>
       <xdr:colOff>476250</xdr:colOff>
       <xdr:row>41</xdr:row>
       <xdr:rowOff>122465</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>46</xdr:col>
+      <xdr:col>45</xdr:col>
       <xdr:colOff>380999</xdr:colOff>
       <xdr:row>58</xdr:row>
       <xdr:rowOff>122464</xdr:rowOff>
@@ -6284,7 +6042,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -6303,13 +6061,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>20</xdr:col>
+      <xdr:col>19</xdr:col>
       <xdr:colOff>72038</xdr:colOff>
       <xdr:row>2</xdr:row>
       <xdr:rowOff>153681</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>40</xdr:col>
+      <xdr:col>39</xdr:col>
       <xdr:colOff>616323</xdr:colOff>
       <xdr:row>31</xdr:row>
       <xdr:rowOff>13608</xdr:rowOff>
@@ -6328,7 +6086,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -6347,105 +6105,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>34</xdr:col>
-      <xdr:colOff>626952</xdr:colOff>
-      <xdr:row>84</xdr:row>
-      <xdr:rowOff>9625</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>38</xdr:col>
-      <xdr:colOff>316505</xdr:colOff>
-      <xdr:row>86</xdr:row>
-      <xdr:rowOff>133077</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="8" name="線吹き出し 1 (枠付き) 7">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000008000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="26770276" y="16594331"/>
-          <a:ext cx="2423788" cy="459628"/>
-        </a:xfrm>
-        <a:prstGeom prst="borderCallout1">
-          <a:avLst>
-            <a:gd name="adj1" fmla="val 43705"/>
-            <a:gd name="adj2" fmla="val 1432"/>
-            <a:gd name="adj3" fmla="val 206357"/>
-            <a:gd name="adj4" fmla="val -16404"/>
-          </a:avLst>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="accent5">
-            <a:lumMod val="20000"/>
-            <a:lumOff val="80000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="50000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200" b="1">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-              <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-            </a:rPr>
-            <a:t>動作電源は</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1200" b="1">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-              <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-            </a:rPr>
-            <a:t>IG-ON</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>41</xdr:col>
+      <xdr:col>40</xdr:col>
       <xdr:colOff>50696</xdr:colOff>
       <xdr:row>71</xdr:row>
       <xdr:rowOff>150131</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>45</xdr:col>
+      <xdr:col>44</xdr:col>
       <xdr:colOff>93355</xdr:colOff>
       <xdr:row>75</xdr:row>
       <xdr:rowOff>125827</xdr:rowOff>
@@ -6528,179 +6194,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>46</xdr:col>
-      <xdr:colOff>267033</xdr:colOff>
-      <xdr:row>84</xdr:row>
-      <xdr:rowOff>9916</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>48</xdr:col>
-      <xdr:colOff>386032</xdr:colOff>
-      <xdr:row>86</xdr:row>
-      <xdr:rowOff>23552</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="15" name="線吹き出し 1 (枠付き) 14">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-00000F000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="34903397" y="16964416"/>
-          <a:ext cx="1504453" cy="360000"/>
-        </a:xfrm>
-        <a:prstGeom prst="borderCallout1">
-          <a:avLst>
-            <a:gd name="adj1" fmla="val 33093"/>
-            <a:gd name="adj2" fmla="val -2637"/>
-            <a:gd name="adj3" fmla="val 244718"/>
-            <a:gd name="adj4" fmla="val -46037"/>
-          </a:avLst>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="accent5">
-            <a:lumMod val="20000"/>
-            <a:lumOff val="80000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="50000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200" b="1">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-              <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-            </a:rPr>
-            <a:t>機能有無判定なし</a:t>
-          </a:r>
-          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200" b="1">
-            <a:solidFill>
-              <a:srgbClr val="FF0000"/>
-            </a:solidFill>
-            <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-            <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-            <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-          </a:endParaRPr>
-        </a:p>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1200" b="1">
-            <a:solidFill>
-              <a:srgbClr val="FF0000"/>
-            </a:solidFill>
-            <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-            <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-            <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-          </a:endParaRPr>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>44</xdr:col>
-      <xdr:colOff>600011</xdr:colOff>
-      <xdr:row>89</xdr:row>
-      <xdr:rowOff>13408</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>45</xdr:col>
-      <xdr:colOff>394101</xdr:colOff>
-      <xdr:row>98</xdr:row>
-      <xdr:rowOff>147205</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="16" name="正方形/長方形 15">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000010000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="33850920" y="17833817"/>
-          <a:ext cx="486817" cy="1692433"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="34925">
-          <a:solidFill>
-            <a:srgbClr val="FF0000"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="50000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>22</xdr:col>
+      <xdr:col>21</xdr:col>
       <xdr:colOff>631237</xdr:colOff>
       <xdr:row>70</xdr:row>
       <xdr:rowOff>166144</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>31</xdr:col>
+      <xdr:col>30</xdr:col>
       <xdr:colOff>182302</xdr:colOff>
       <xdr:row>73</xdr:row>
       <xdr:rowOff>13074</xdr:rowOff>
@@ -6851,13 +6351,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>549088</xdr:colOff>
-      <xdr:row>32</xdr:row>
+      <xdr:row>20</xdr:row>
       <xdr:rowOff>111261</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
       <xdr:colOff>276944</xdr:colOff>
-      <xdr:row>37</xdr:row>
+      <xdr:row>25</xdr:row>
       <xdr:rowOff>89645</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -6974,13 +6474,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>21</xdr:col>
+      <xdr:col>20</xdr:col>
       <xdr:colOff>103599</xdr:colOff>
       <xdr:row>62</xdr:row>
       <xdr:rowOff>149063</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>24</xdr:col>
+      <xdr:col>23</xdr:col>
       <xdr:colOff>421822</xdr:colOff>
       <xdr:row>68</xdr:row>
       <xdr:rowOff>163285</xdr:rowOff>
@@ -7040,13 +6540,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>34</xdr:col>
+      <xdr:col>33</xdr:col>
       <xdr:colOff>310614</xdr:colOff>
       <xdr:row>62</xdr:row>
       <xdr:rowOff>145676</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>37</xdr:col>
+      <xdr:col>36</xdr:col>
       <xdr:colOff>352985</xdr:colOff>
       <xdr:row>68</xdr:row>
       <xdr:rowOff>140872</xdr:rowOff>
@@ -7106,13 +6606,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>37</xdr:col>
+      <xdr:col>36</xdr:col>
       <xdr:colOff>357641</xdr:colOff>
       <xdr:row>62</xdr:row>
       <xdr:rowOff>143948</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>40</xdr:col>
+      <xdr:col>39</xdr:col>
       <xdr:colOff>389804</xdr:colOff>
       <xdr:row>68</xdr:row>
       <xdr:rowOff>167285</xdr:rowOff>
@@ -7172,13 +6672,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>30</xdr:col>
+      <xdr:col>29</xdr:col>
       <xdr:colOff>324971</xdr:colOff>
       <xdr:row>48</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>32</xdr:col>
+      <xdr:col>31</xdr:col>
       <xdr:colOff>190500</xdr:colOff>
       <xdr:row>58</xdr:row>
       <xdr:rowOff>41131</xdr:rowOff>
@@ -7238,13 +6738,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>31</xdr:col>
+      <xdr:col>30</xdr:col>
       <xdr:colOff>450273</xdr:colOff>
       <xdr:row>42</xdr:row>
       <xdr:rowOff>73294</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>35</xdr:col>
+      <xdr:col>34</xdr:col>
       <xdr:colOff>139828</xdr:colOff>
       <xdr:row>45</xdr:row>
       <xdr:rowOff>37462</xdr:rowOff>
@@ -7330,13 +6830,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>36</xdr:col>
+      <xdr:col>35</xdr:col>
       <xdr:colOff>5381</xdr:colOff>
       <xdr:row>70</xdr:row>
       <xdr:rowOff>132598</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>38</xdr:col>
+      <xdr:col>37</xdr:col>
       <xdr:colOff>599876</xdr:colOff>
       <xdr:row>74</xdr:row>
       <xdr:rowOff>44823</xdr:rowOff>
@@ -7433,13 +6933,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>20</xdr:col>
+      <xdr:col>19</xdr:col>
       <xdr:colOff>24120</xdr:colOff>
       <xdr:row>10</xdr:row>
       <xdr:rowOff>626344</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>40</xdr:col>
+      <xdr:col>39</xdr:col>
       <xdr:colOff>309869</xdr:colOff>
       <xdr:row>11</xdr:row>
       <xdr:rowOff>168088</xdr:rowOff>
@@ -7499,13 +6999,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>40</xdr:col>
+      <xdr:col>39</xdr:col>
       <xdr:colOff>593912</xdr:colOff>
       <xdr:row>10</xdr:row>
       <xdr:rowOff>560294</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>42</xdr:col>
+      <xdr:col>41</xdr:col>
       <xdr:colOff>448235</xdr:colOff>
       <xdr:row>11</xdr:row>
       <xdr:rowOff>102265</xdr:rowOff>
@@ -7599,536 +7099,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>22</xdr:col>
-      <xdr:colOff>241888</xdr:colOff>
-      <xdr:row>114</xdr:row>
-      <xdr:rowOff>81406</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>31</xdr:col>
-      <xdr:colOff>76872</xdr:colOff>
-      <xdr:row>116</xdr:row>
-      <xdr:rowOff>93283</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="34" name="線吹き出し 1 (枠付き) 33">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000022000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="18062297" y="21884997"/>
-          <a:ext cx="6069530" cy="358241"/>
-        </a:xfrm>
-        <a:prstGeom prst="borderCallout1">
-          <a:avLst>
-            <a:gd name="adj1" fmla="val 42429"/>
-            <a:gd name="adj2" fmla="val -3670"/>
-            <a:gd name="adj3" fmla="val -95894"/>
-            <a:gd name="adj4" fmla="val -6581"/>
-          </a:avLst>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="accent5">
-            <a:lumMod val="20000"/>
-            <a:lumOff val="80000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="50000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200" b="1">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-              <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-            </a:rPr>
-            <a:t>本機能の信号が</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1200" b="1">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-              <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-            </a:rPr>
-            <a:t>RW</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200" b="1">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-              <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-            </a:rPr>
-            <a:t>仕様書にも記載されていないため、</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1200" b="1">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-              <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-            </a:rPr>
-            <a:t></a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200" b="1">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-              <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-            </a:rPr>
-            <a:t>該当する</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1200" b="1">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-              <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-            </a:rPr>
-            <a:t>RW</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200" b="1">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-              <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-            </a:rPr>
-            <a:t>信号はなし</a:t>
-          </a:r>
-          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1200" b="1">
-            <a:solidFill>
-              <a:schemeClr val="tx1"/>
-            </a:solidFill>
-            <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-            <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-            <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-          </a:endParaRPr>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>20</xdr:col>
-      <xdr:colOff>665513</xdr:colOff>
-      <xdr:row>105</xdr:row>
-      <xdr:rowOff>64325</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>24</xdr:col>
-      <xdr:colOff>665512</xdr:colOff>
-      <xdr:row>112</xdr:row>
-      <xdr:rowOff>64325</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="35" name="正方形/長方形 34">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000023000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="17100468" y="20309280"/>
-          <a:ext cx="2770908" cy="1212272"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="34925">
-          <a:solidFill>
-            <a:srgbClr val="FF0000"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="50000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>33</xdr:col>
-      <xdr:colOff>122467</xdr:colOff>
-      <xdr:row>105</xdr:row>
-      <xdr:rowOff>50719</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>35</xdr:col>
-      <xdr:colOff>352549</xdr:colOff>
-      <xdr:row>112</xdr:row>
-      <xdr:rowOff>23504</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="36" name="正方形/長方形 35">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000024000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="25562876" y="20295674"/>
-          <a:ext cx="1615537" cy="1185057"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="34925">
-          <a:solidFill>
-            <a:srgbClr val="FF0000"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="50000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>34</xdr:col>
-      <xdr:colOff>225445</xdr:colOff>
-      <xdr:row>114</xdr:row>
-      <xdr:rowOff>45770</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>38</xdr:col>
-      <xdr:colOff>517966</xdr:colOff>
-      <xdr:row>117</xdr:row>
-      <xdr:rowOff>12151</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="37" name="線吹き出し 1 (枠付き) 36">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000025000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="26358581" y="21849361"/>
-          <a:ext cx="3063430" cy="485926"/>
-        </a:xfrm>
-        <a:prstGeom prst="borderCallout1">
-          <a:avLst>
-            <a:gd name="adj1" fmla="val 45277"/>
-            <a:gd name="adj2" fmla="val -3670"/>
-            <a:gd name="adj3" fmla="val -63176"/>
-            <a:gd name="adj4" fmla="val -22413"/>
-          </a:avLst>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="accent5">
-            <a:lumMod val="20000"/>
-            <a:lumOff val="80000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="50000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200" b="1">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-              <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-            </a:rPr>
-            <a:t>初期値は表示無し</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>35</xdr:col>
-      <xdr:colOff>393371</xdr:colOff>
-      <xdr:row>105</xdr:row>
-      <xdr:rowOff>50716</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>39</xdr:col>
-      <xdr:colOff>13607</xdr:colOff>
-      <xdr:row>112</xdr:row>
-      <xdr:rowOff>9896</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="38" name="正方形/長方形 37">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000026000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="27219235" y="20295671"/>
-          <a:ext cx="2391145" cy="1171452"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="34925">
-          <a:solidFill>
-            <a:srgbClr val="FF0000"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="50000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>39</xdr:col>
-      <xdr:colOff>420584</xdr:colOff>
-      <xdr:row>114</xdr:row>
-      <xdr:rowOff>64327</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>43</xdr:col>
-      <xdr:colOff>460041</xdr:colOff>
-      <xdr:row>118</xdr:row>
-      <xdr:rowOff>40023</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="39" name="線吹き出し 1 (枠付き) 38">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000027000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="30017357" y="21867918"/>
-          <a:ext cx="2810366" cy="668423"/>
-        </a:xfrm>
-        <a:prstGeom prst="borderCallout1">
-          <a:avLst>
-            <a:gd name="adj1" fmla="val 38295"/>
-            <a:gd name="adj2" fmla="val -1002"/>
-            <a:gd name="adj3" fmla="val -46376"/>
-            <a:gd name="adj4" fmla="val -35357"/>
-          </a:avLst>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="accent5">
-            <a:lumMod val="20000"/>
-            <a:lumOff val="80000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="50000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200" b="1">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-              <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-            </a:rPr>
-            <a:t>通信途絶時は表示無し</a:t>
-          </a:r>
-          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1200" b="1">
-            <a:solidFill>
-              <a:schemeClr val="tx1"/>
-            </a:solidFill>
-            <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-            <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-            <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-          </a:endParaRPr>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
       <xdr:col>10</xdr:col>
       <xdr:colOff>299356</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>13607</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>12</xdr:col>
+      <xdr:col>11</xdr:col>
       <xdr:colOff>616322</xdr:colOff>
       <xdr:row>3</xdr:row>
       <xdr:rowOff>19821</xdr:rowOff>
@@ -8239,814 +7216,6 @@
               <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
             </a:rPr>
             <a:t>を使用する</a:t>
-          </a:r>
-          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1200" b="1">
-            <a:solidFill>
-              <a:schemeClr val="tx1"/>
-            </a:solidFill>
-            <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-            <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-            <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-          </a:endParaRPr>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>33</xdr:col>
-      <xdr:colOff>419714</xdr:colOff>
-      <xdr:row>89</xdr:row>
-      <xdr:rowOff>100852</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>35</xdr:col>
-      <xdr:colOff>118758</xdr:colOff>
-      <xdr:row>98</xdr:row>
-      <xdr:rowOff>147205</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="42" name="正方形/長方形 41">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-00002A000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="25879479" y="17525999"/>
-          <a:ext cx="1066161" cy="1559147"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="34925">
-          <a:solidFill>
-            <a:srgbClr val="FF0000"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="50000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>20</xdr:col>
-      <xdr:colOff>57051</xdr:colOff>
-      <xdr:row>94</xdr:row>
-      <xdr:rowOff>22412</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>50</xdr:col>
-      <xdr:colOff>338215</xdr:colOff>
-      <xdr:row>96</xdr:row>
-      <xdr:rowOff>84046</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="40" name="正方形/長方形 39">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000028000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="16682506" y="18708730"/>
-          <a:ext cx="21062982" cy="407998"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="34925">
-          <a:solidFill>
-            <a:srgbClr val="FF0000"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="50000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>20</xdr:col>
-      <xdr:colOff>57051</xdr:colOff>
-      <xdr:row>96</xdr:row>
-      <xdr:rowOff>107577</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>50</xdr:col>
-      <xdr:colOff>333733</xdr:colOff>
-      <xdr:row>99</xdr:row>
-      <xdr:rowOff>1122</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="43" name="正方形/長方形 42">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-00002B000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="16682506" y="19140259"/>
-          <a:ext cx="21058500" cy="413090"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="34925">
-          <a:solidFill>
-            <a:srgbClr val="FF0000"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="50000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>807179</xdr:colOff>
-      <xdr:row>91</xdr:row>
-      <xdr:rowOff>134471</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>19</xdr:col>
-      <xdr:colOff>173312</xdr:colOff>
-      <xdr:row>94</xdr:row>
-      <xdr:rowOff>89835</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="46" name="線吹き出し 1 (枠付き) 45">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-00002E000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="14384634" y="18301244"/>
-          <a:ext cx="1721405" cy="474909"/>
-        </a:xfrm>
-        <a:prstGeom prst="borderCallout1">
-          <a:avLst>
-            <a:gd name="adj1" fmla="val 60771"/>
-            <a:gd name="adj2" fmla="val 101295"/>
-            <a:gd name="adj3" fmla="val 133217"/>
-            <a:gd name="adj4" fmla="val 133391"/>
-          </a:avLst>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="accent5">
-            <a:lumMod val="20000"/>
-            <a:lumOff val="80000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="50000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200" b="1">
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-              <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-            </a:rPr>
-            <a:t>要求</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1200" b="1">
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-              <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-            </a:rPr>
-            <a:t>No.2</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200" b="1">
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-              <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-            </a:rPr>
-            <a:t>削除</a:t>
-          </a:r>
-          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1200" b="1">
-            <a:solidFill>
-              <a:srgbClr val="FF0000"/>
-            </a:solidFill>
-            <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-            <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-            <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-          </a:endParaRPr>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>67017</xdr:colOff>
-      <xdr:row>98</xdr:row>
-      <xdr:rowOff>54471</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>19</xdr:col>
-      <xdr:colOff>249440</xdr:colOff>
-      <xdr:row>101</xdr:row>
-      <xdr:rowOff>9836</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="47" name="線吹き出し 1 (枠付き) 46">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-00002F000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="14475744" y="19433516"/>
-          <a:ext cx="1706423" cy="474911"/>
-        </a:xfrm>
-        <a:prstGeom prst="borderCallout1">
-          <a:avLst>
-            <a:gd name="adj1" fmla="val 60771"/>
-            <a:gd name="adj2" fmla="val 101295"/>
-            <a:gd name="adj3" fmla="val -25255"/>
-            <a:gd name="adj4" fmla="val 128768"/>
-          </a:avLst>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="accent5">
-            <a:lumMod val="20000"/>
-            <a:lumOff val="80000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="50000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200" b="1">
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-              <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-            </a:rPr>
-            <a:t>要求</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1200" b="1">
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-              <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-            </a:rPr>
-            <a:t>No.3</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200" b="1">
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-              <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-            </a:rPr>
-            <a:t>追加</a:t>
-          </a:r>
-          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1200" b="1">
-            <a:solidFill>
-              <a:srgbClr val="FF0000"/>
-            </a:solidFill>
-            <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-            <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-            <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-          </a:endParaRPr>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>29</xdr:col>
-      <xdr:colOff>257736</xdr:colOff>
-      <xdr:row>100</xdr:row>
-      <xdr:rowOff>123263</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>34</xdr:col>
-      <xdr:colOff>267389</xdr:colOff>
-      <xdr:row>103</xdr:row>
-      <xdr:rowOff>78627</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="48" name="線吹き出し 1 (枠付き) 47">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000030000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="22983265" y="19397381"/>
-          <a:ext cx="3427448" cy="459628"/>
-        </a:xfrm>
-        <a:prstGeom prst="borderCallout1">
-          <a:avLst>
-            <a:gd name="adj1" fmla="val 60771"/>
-            <a:gd name="adj2" fmla="val 101295"/>
-            <a:gd name="adj3" fmla="val -106551"/>
-            <a:gd name="adj4" fmla="val 113282"/>
-          </a:avLst>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="accent5">
-            <a:lumMod val="20000"/>
-            <a:lumOff val="80000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="50000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1200" b="1">
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-              <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-            </a:rPr>
-            <a:t>No2</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200" b="1">
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-              <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-            </a:rPr>
-            <a:t>と実施条件、動作電源は変更なし</a:t>
-          </a:r>
-          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1200" b="1">
-            <a:solidFill>
-              <a:srgbClr val="FF0000"/>
-            </a:solidFill>
-            <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-            <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-            <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-          </a:endParaRPr>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>20</xdr:col>
-      <xdr:colOff>22412</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>134472</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>23</xdr:col>
-      <xdr:colOff>639108</xdr:colOff>
-      <xdr:row>36</xdr:row>
-      <xdr:rowOff>8505</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="図 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000003000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="16595912" y="7810501"/>
-          <a:ext cx="2667372" cy="714475"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>20</xdr:col>
-      <xdr:colOff>190500</xdr:colOff>
-      <xdr:row>121</xdr:row>
-      <xdr:rowOff>134471</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>24</xdr:col>
-      <xdr:colOff>609480</xdr:colOff>
-      <xdr:row>127</xdr:row>
-      <xdr:rowOff>107154</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="9" name="図 8">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000009000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="16764000" y="22938442"/>
-          <a:ext cx="3153215" cy="981212"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>24</xdr:col>
-      <xdr:colOff>357004</xdr:colOff>
-      <xdr:row>32</xdr:row>
-      <xdr:rowOff>111968</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>26</xdr:col>
-      <xdr:colOff>616324</xdr:colOff>
-      <xdr:row>34</xdr:row>
-      <xdr:rowOff>123845</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="44" name="線吹き出し 1 (枠付き) 43">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-00002C000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="19664739" y="7956086"/>
-          <a:ext cx="1626438" cy="348053"/>
-        </a:xfrm>
-        <a:prstGeom prst="borderCallout1">
-          <a:avLst>
-            <a:gd name="adj1" fmla="val 42429"/>
-            <a:gd name="adj2" fmla="val -3670"/>
-            <a:gd name="adj3" fmla="val 77964"/>
-            <a:gd name="adj4" fmla="val -38685"/>
-          </a:avLst>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="accent5">
-            <a:lumMod val="20000"/>
-            <a:lumOff val="80000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="50000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1200" b="1">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-              <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-            </a:rPr>
-            <a:t>TT</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200" b="1">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-              <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-            </a:rPr>
-            <a:t>は要求なし</a:t>
-          </a:r>
-          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1200" b="1">
-            <a:solidFill>
-              <a:schemeClr val="tx1"/>
-            </a:solidFill>
-            <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-            <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-            <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-          </a:endParaRPr>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>25</xdr:col>
-      <xdr:colOff>16345</xdr:colOff>
-      <xdr:row>123</xdr:row>
-      <xdr:rowOff>141103</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>27</xdr:col>
-      <xdr:colOff>219636</xdr:colOff>
-      <xdr:row>125</xdr:row>
-      <xdr:rowOff>152979</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="45" name="線吹き出し 1 (枠付き) 44">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-00002D000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="20007639" y="23281250"/>
-          <a:ext cx="1570409" cy="348053"/>
-        </a:xfrm>
-        <a:prstGeom prst="borderCallout1">
-          <a:avLst>
-            <a:gd name="adj1" fmla="val 42429"/>
-            <a:gd name="adj2" fmla="val -3670"/>
-            <a:gd name="adj3" fmla="val 81184"/>
-            <a:gd name="adj4" fmla="val -34551"/>
-          </a:avLst>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="accent5">
-            <a:lumMod val="20000"/>
-            <a:lumOff val="80000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="50000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1200" b="1">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-              <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-            </a:rPr>
-            <a:t>VMID</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200" b="1">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-              <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-            </a:rPr>
-            <a:t>は要求なし</a:t>
           </a:r>
           <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1200" b="1">
             <a:solidFill>
@@ -9353,13 +7522,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="B2:R13"/>
-  <sheetFormatPr defaultRowHeight="13"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="4.453125" customWidth="1"/>
+    <col min="1" max="1" width="4.5" customWidth="1"/>
     <col min="2" max="2" width="9" style="9" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="69.453125" customWidth="1"/>
-    <col min="5" max="6" width="12.7265625" customWidth="1"/>
-    <col min="7" max="18" width="13.08984375" customWidth="1"/>
+    <col min="4" max="4" width="69.5" customWidth="1"/>
+    <col min="5" max="6" width="12.75" customWidth="1"/>
+    <col min="7" max="18" width="13.125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:18" ht="25.5" customHeight="1">
@@ -9370,18 +7539,18 @@
       <c r="H2" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="I2" s="233" t="s">
+      <c r="I2" s="226" t="s">
         <v>14</v>
       </c>
-      <c r="J2" s="233"/>
-      <c r="K2" s="233"/>
-      <c r="L2" s="233"/>
-      <c r="M2" s="233"/>
-      <c r="N2" s="233"/>
-      <c r="O2" s="233"/>
-      <c r="P2" s="233"/>
-      <c r="Q2" s="233"/>
-      <c r="R2" s="233"/>
+      <c r="J2" s="226"/>
+      <c r="K2" s="226"/>
+      <c r="L2" s="226"/>
+      <c r="M2" s="226"/>
+      <c r="N2" s="226"/>
+      <c r="O2" s="226"/>
+      <c r="P2" s="226"/>
+      <c r="Q2" s="226"/>
+      <c r="R2" s="226"/>
     </row>
     <row r="3" spans="2:18" ht="25.5" customHeight="1">
       <c r="C3" s="6"/>
@@ -9394,25 +7563,25 @@
       <c r="H3" s="8" t="s">
         <v>194</v>
       </c>
-      <c r="I3" s="234" t="s">
+      <c r="I3" s="227" t="s">
         <v>221</v>
       </c>
-      <c r="J3" s="235"/>
-      <c r="K3" s="235"/>
-      <c r="L3" s="235"/>
-      <c r="M3" s="235"/>
-      <c r="N3" s="235"/>
-      <c r="O3" s="235"/>
-      <c r="P3" s="235"/>
-      <c r="Q3" s="235"/>
-      <c r="R3" s="235"/>
+      <c r="J3" s="228"/>
+      <c r="K3" s="228"/>
+      <c r="L3" s="228"/>
+      <c r="M3" s="228"/>
+      <c r="N3" s="228"/>
+      <c r="O3" s="228"/>
+      <c r="P3" s="228"/>
+      <c r="Q3" s="228"/>
+      <c r="R3" s="228"/>
     </row>
     <row r="4" spans="2:18" ht="25.5" customHeight="1">
       <c r="C4" s="6"/>
       <c r="D4" s="6"/>
       <c r="E4" s="23" t="str">
         <f>DGET(B8:C14,"Ver.",H4:H5)</f>
-        <v>1.0.0</v>
+        <v>1.1.0</v>
       </c>
       <c r="F4" s="6"/>
       <c r="H4" s="9" t="s">
@@ -9426,37 +7595,37 @@
       <c r="F5" s="6"/>
       <c r="H5" s="11">
         <f>MAX(B9:B14)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="2:18" ht="13.5" thickBot="1"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="2:18" ht="14.25" thickBot="1"/>
     <row r="7" spans="2:18">
-      <c r="C7" s="227" t="s">
-        <v>0</v>
-      </c>
-      <c r="D7" s="228"/>
-      <c r="E7" s="229" t="s">
+      <c r="C7" s="220" t="s">
+        <v>0</v>
+      </c>
+      <c r="D7" s="221"/>
+      <c r="E7" s="222" t="s">
         <v>2</v>
       </c>
-      <c r="F7" s="229"/>
-      <c r="G7" s="230" t="s">
+      <c r="F7" s="222"/>
+      <c r="G7" s="223" t="s">
         <v>5</v>
       </c>
-      <c r="H7" s="230"/>
-      <c r="I7" s="230"/>
-      <c r="J7" s="230"/>
-      <c r="K7" s="230"/>
-      <c r="L7" s="230"/>
-      <c r="M7" s="231" t="s">
+      <c r="H7" s="223"/>
+      <c r="I7" s="223"/>
+      <c r="J7" s="223"/>
+      <c r="K7" s="223"/>
+      <c r="L7" s="223"/>
+      <c r="M7" s="224" t="s">
         <v>12</v>
       </c>
-      <c r="N7" s="231"/>
-      <c r="O7" s="231"/>
-      <c r="P7" s="231"/>
-      <c r="Q7" s="231"/>
-      <c r="R7" s="232"/>
-    </row>
-    <row r="8" spans="2:18" ht="26.5" thickBot="1">
+      <c r="N7" s="224"/>
+      <c r="O7" s="224"/>
+      <c r="P7" s="224"/>
+      <c r="Q7" s="224"/>
+      <c r="R7" s="225"/>
+    </row>
+    <row r="8" spans="2:18" ht="27.75" thickBot="1">
       <c r="B8" s="9" t="s">
         <v>97</v>
       </c>
@@ -9509,7 +7678,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="2:18" ht="169.5" thickTop="1">
+    <row r="9" spans="2:18" ht="176.25" thickTop="1">
       <c r="B9" s="9">
         <f>IF(C9=0,0,ROW()-ROW($B$8))</f>
         <v>1</v>
@@ -9517,8 +7686,8 @@
       <c r="C9" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="D9" s="223" t="s">
-        <v>289</v>
+      <c r="D9" s="218" t="s">
+        <v>261</v>
       </c>
       <c r="E9" s="13" t="s">
         <v>32</v>
@@ -9545,37 +7714,61 @@
         <v>32</v>
       </c>
       <c r="M9" s="13"/>
-      <c r="N9" s="217"/>
+      <c r="N9" s="215"/>
       <c r="O9" s="13"/>
-      <c r="P9" s="217"/>
+      <c r="P9" s="215"/>
       <c r="Q9" s="1" t="s">
-        <v>286</v>
-      </c>
-      <c r="R9" s="224">
+        <v>260</v>
+      </c>
+      <c r="R9" s="219">
         <v>44264</v>
       </c>
     </row>
-    <row r="10" spans="2:18">
+    <row r="10" spans="2:18" ht="94.5">
       <c r="B10" s="9">
         <f t="shared" ref="B10:B13" si="0">IF(C10=0,0,ROW()-ROW($B$8))</f>
-        <v>0</v>
-      </c>
-      <c r="C10" s="2"/>
-      <c r="D10" s="223"/>
-      <c r="E10" s="222"/>
-      <c r="F10" s="222"/>
-      <c r="G10" s="222"/>
-      <c r="H10" s="222"/>
-      <c r="I10" s="222"/>
-      <c r="J10" s="222"/>
-      <c r="K10" s="222"/>
-      <c r="L10" s="222"/>
-      <c r="M10" s="1"/>
-      <c r="N10" s="1"/>
-      <c r="O10" s="1"/>
-      <c r="P10" s="1"/>
-      <c r="Q10" s="1"/>
-      <c r="R10" s="224"/>
+        <v>2</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>263</v>
+      </c>
+      <c r="D10" s="218" t="s">
+        <v>266</v>
+      </c>
+      <c r="E10" s="217" t="s">
+        <v>32</v>
+      </c>
+      <c r="F10" s="217" t="s">
+        <v>264</v>
+      </c>
+      <c r="G10" s="217"/>
+      <c r="H10" s="217"/>
+      <c r="I10" s="217"/>
+      <c r="J10" s="217"/>
+      <c r="K10" s="217" t="s">
+        <v>265</v>
+      </c>
+      <c r="L10" s="215">
+        <v>45839</v>
+      </c>
+      <c r="M10" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="N10" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="O10" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="P10" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q10" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="R10" s="219" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="11" spans="2:18">
       <c r="B11" s="9">
@@ -9583,21 +7776,21 @@
         <v>0</v>
       </c>
       <c r="C11" s="2"/>
-      <c r="D11" s="223"/>
-      <c r="E11" s="222"/>
-      <c r="F11" s="222"/>
-      <c r="G11" s="222"/>
-      <c r="H11" s="222"/>
-      <c r="I11" s="222"/>
-      <c r="J11" s="222"/>
-      <c r="K11" s="222"/>
-      <c r="L11" s="222"/>
+      <c r="D11" s="218"/>
+      <c r="E11" s="217"/>
+      <c r="F11" s="217"/>
+      <c r="G11" s="217"/>
+      <c r="H11" s="217"/>
+      <c r="I11" s="217"/>
+      <c r="J11" s="217"/>
+      <c r="K11" s="217"/>
+      <c r="L11" s="217"/>
       <c r="M11" s="1"/>
       <c r="N11" s="1"/>
       <c r="O11" s="1"/>
       <c r="P11" s="1"/>
       <c r="Q11" s="1"/>
-      <c r="R11" s="224"/>
+      <c r="R11" s="219"/>
     </row>
     <row r="12" spans="2:18">
       <c r="B12" s="9">
@@ -9605,23 +7798,23 @@
         <v>0</v>
       </c>
       <c r="C12" s="2"/>
-      <c r="D12" s="223"/>
-      <c r="E12" s="222"/>
-      <c r="F12" s="222"/>
-      <c r="G12" s="222"/>
-      <c r="H12" s="222"/>
-      <c r="I12" s="222"/>
-      <c r="J12" s="222"/>
-      <c r="K12" s="222"/>
-      <c r="L12" s="222"/>
+      <c r="D12" s="218"/>
+      <c r="E12" s="217"/>
+      <c r="F12" s="217"/>
+      <c r="G12" s="217"/>
+      <c r="H12" s="217"/>
+      <c r="I12" s="217"/>
+      <c r="J12" s="217"/>
+      <c r="K12" s="217"/>
+      <c r="L12" s="217"/>
       <c r="M12" s="1"/>
       <c r="N12" s="1"/>
       <c r="O12" s="1"/>
       <c r="P12" s="1"/>
       <c r="Q12" s="1"/>
-      <c r="R12" s="224"/>
-    </row>
-    <row r="13" spans="2:18" ht="13.5" thickBot="1">
+      <c r="R12" s="219"/>
+    </row>
+    <row r="13" spans="2:18" ht="14.25" thickBot="1">
       <c r="B13" s="9">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -9668,11 +7861,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="B2:E39"/>
-  <sheetFormatPr defaultRowHeight="13"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="2" max="2" width="4.6328125" customWidth="1"/>
-    <col min="3" max="3" width="3.453125" customWidth="1"/>
-    <col min="4" max="4" width="17.453125" customWidth="1"/>
+    <col min="2" max="2" width="4.625" customWidth="1"/>
+    <col min="3" max="3" width="3.5" customWidth="1"/>
+    <col min="4" max="4" width="17.5" customWidth="1"/>
     <col min="5" max="5" width="106" customWidth="1"/>
   </cols>
   <sheetData>
@@ -9686,13 +7879,13 @@
         <v>144</v>
       </c>
     </row>
-    <row r="6" spans="2:5" ht="13.5" thickBot="1">
+    <row r="6" spans="2:5" ht="14.25" thickBot="1">
       <c r="B6" s="156" t="s">
         <v>135</v>
       </c>
       <c r="C6" s="156"/>
     </row>
-    <row r="7" spans="2:5" ht="13.5" thickBot="1">
+    <row r="7" spans="2:5" ht="14.25" thickBot="1">
       <c r="C7" s="77" t="s">
         <v>137</v>
       </c>
@@ -9712,7 +7905,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="9" spans="2:5" ht="26">
+    <row r="9" spans="2:5" ht="27">
       <c r="C9" s="166">
         <v>1</v>
       </c>
@@ -9723,7 +7916,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="10" spans="2:5" ht="13.5" thickBot="1">
+    <row r="10" spans="2:5" ht="14.25" thickBot="1">
       <c r="C10" s="164"/>
       <c r="D10" s="88"/>
       <c r="E10" s="5"/>
@@ -9731,14 +7924,14 @@
     <row r="11" spans="2:5">
       <c r="C11" s="162"/>
     </row>
-    <row r="12" spans="2:5" ht="13.5" thickBot="1">
+    <row r="12" spans="2:5" ht="14.25" thickBot="1">
       <c r="B12" s="157" t="s">
         <v>136</v>
       </c>
       <c r="C12" s="84"/>
       <c r="D12" s="84"/>
     </row>
-    <row r="13" spans="2:5" ht="13.5" thickBot="1">
+    <row r="13" spans="2:5" ht="14.25" thickBot="1">
       <c r="B13" s="158"/>
       <c r="C13" s="163" t="s">
         <v>137</v>
@@ -9750,7 +7943,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="14" spans="2:5" ht="13.5" thickTop="1">
+    <row r="14" spans="2:5" ht="14.25" thickTop="1">
       <c r="C14" s="160">
         <v>0</v>
       </c>
@@ -9827,17 +8020,17 @@
         <v>188</v>
       </c>
     </row>
-    <row r="21" spans="2:5" ht="13.5" thickBot="1">
+    <row r="21" spans="2:5" ht="14.25" thickBot="1">
       <c r="C21" s="164"/>
       <c r="D21" s="88"/>
       <c r="E21" s="5"/>
     </row>
-    <row r="24" spans="2:5" ht="13.5" thickBot="1">
+    <row r="24" spans="2:5" ht="14.25" thickBot="1">
       <c r="B24" s="156" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="25" spans="2:5" ht="13.5" thickBot="1">
+    <row r="25" spans="2:5" ht="14.25" thickBot="1">
       <c r="C25" s="163" t="s">
         <v>137</v>
       </c>
@@ -9924,26 +8117,26 @@
       <c r="D33" s="87"/>
       <c r="E33" s="76"/>
     </row>
-    <row r="34" spans="2:5" ht="13.5" thickBot="1">
+    <row r="34" spans="2:5" ht="14.25" thickBot="1">
       <c r="C34" s="164"/>
       <c r="D34" s="88"/>
       <c r="E34" s="5"/>
     </row>
-    <row r="37" spans="2:5" ht="13.5" thickBot="1">
+    <row r="37" spans="2:5" ht="14.25" thickBot="1">
       <c r="B37" s="156" t="s">
         <v>184</v>
       </c>
     </row>
     <row r="38" spans="2:5">
-      <c r="C38" s="236"/>
-      <c r="D38" s="237"/>
+      <c r="C38" s="229"/>
+      <c r="D38" s="230"/>
       <c r="E38" s="113" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="39" spans="2:5" ht="13.5" thickBot="1">
-      <c r="C39" s="238"/>
-      <c r="D39" s="239"/>
+    <row r="39" spans="2:5" ht="14.25" thickBot="1">
+      <c r="C39" s="231"/>
+      <c r="D39" s="232"/>
       <c r="E39" s="5" t="s">
         <v>124</v>
       </c>
@@ -9972,24 +8165,24 @@
     <tabColor rgb="FFCCFFCC"/>
   </sheetPr>
   <dimension ref="B1:N37"/>
-  <sheetFormatPr defaultRowHeight="13"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="2" max="2" width="3.7265625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.08984375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.08984375" bestFit="1" customWidth="1"/>
-    <col min="6" max="8" width="26.7265625" customWidth="1"/>
-    <col min="9" max="9" width="20.90625" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="3.75" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.125" bestFit="1" customWidth="1"/>
+    <col min="6" max="8" width="26.75" customWidth="1"/>
+    <col min="9" max="9" width="20.875" hidden="1" customWidth="1"/>
     <col min="10" max="14" width="9" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:14" ht="13.5" thickBot="1"/>
+    <row r="1" spans="2:14" ht="14.25" thickBot="1"/>
     <row r="2" spans="2:14">
-      <c r="B2" s="240" t="s">
+      <c r="B2" s="258" t="s">
         <v>19</v>
       </c>
-      <c r="C2" s="241"/>
+      <c r="C2" s="259"/>
       <c r="D2" s="246" t="s">
-        <v>283</v>
+        <v>267</v>
       </c>
       <c r="E2" s="247"/>
       <c r="F2" s="247"/>
@@ -9997,19 +8190,19 @@
       <c r="H2" s="248"/>
     </row>
     <row r="3" spans="2:14">
-      <c r="B3" s="242" t="s">
+      <c r="B3" s="233" t="s">
         <v>121</v>
       </c>
-      <c r="C3" s="243"/>
-      <c r="D3" s="258" t="s">
-        <v>284</v>
-      </c>
-      <c r="E3" s="259"/>
-      <c r="F3" s="259"/>
-      <c r="G3" s="259"/>
-      <c r="H3" s="260"/>
-    </row>
-    <row r="4" spans="2:14" ht="13.5" thickBot="1">
+      <c r="C3" s="234"/>
+      <c r="D3" s="255" t="s">
+        <v>268</v>
+      </c>
+      <c r="E3" s="256"/>
+      <c r="F3" s="256"/>
+      <c r="G3" s="256"/>
+      <c r="H3" s="257"/>
+    </row>
+    <row r="4" spans="2:14" ht="14.25" thickBot="1">
       <c r="B4" s="244" t="s">
         <v>18</v>
       </c>
@@ -10023,17 +8216,17 @@
       <c r="G4" s="250"/>
       <c r="H4" s="251"/>
     </row>
-    <row r="5" spans="2:14" ht="13.5" thickBot="1">
+    <row r="5" spans="2:14" ht="14.25" thickBot="1">
       <c r="D5" t="str">
         <f ca="1">IF(LEN(表紙!D3&amp;".c") = LENB(表紙!D3&amp;".c"),"※モジュール名 全角チェックOK","※モジュール名 全角チェックNG：ファイル名に全角文字が使用されています！")</f>
         <v>※モジュール名 全角チェックOK</v>
       </c>
     </row>
     <row r="6" spans="2:14">
-      <c r="B6" s="240" t="s">
+      <c r="B6" s="258" t="s">
         <v>41</v>
       </c>
-      <c r="C6" s="241"/>
+      <c r="C6" s="259"/>
       <c r="D6" s="252" t="str">
         <f ca="1">MID(D4, LEN("alert_") + 1, FIND("-",D4,1) - LEN("alert_") - 1)</f>
         <v>S_SCB</v>
@@ -10044,61 +8237,61 @@
       <c r="H6" s="254"/>
     </row>
     <row r="7" spans="2:14">
-      <c r="B7" s="242" t="s">
+      <c r="B7" s="233" t="s">
         <v>42</v>
       </c>
-      <c r="C7" s="243"/>
-      <c r="D7" s="255">
+      <c r="C7" s="234"/>
+      <c r="D7" s="235">
         <f>COUNTA($D$13:$D$37)</f>
         <v>1</v>
       </c>
-      <c r="E7" s="256"/>
-      <c r="F7" s="256"/>
-      <c r="G7" s="256"/>
-      <c r="H7" s="257"/>
+      <c r="E7" s="236"/>
+      <c r="F7" s="236"/>
+      <c r="G7" s="236"/>
+      <c r="H7" s="237"/>
     </row>
     <row r="8" spans="2:14">
-      <c r="B8" s="242" t="s">
+      <c r="B8" s="233" t="s">
         <v>100</v>
       </c>
-      <c r="C8" s="243"/>
-      <c r="D8" s="255" t="str">
+      <c r="C8" s="234"/>
+      <c r="D8" s="235" t="str">
         <f ca="1">"st_gp_ALERT_"&amp;UPPER(D6)&amp;"_MTRX"</f>
         <v>st_gp_ALERT_S_SCB_MTRX</v>
       </c>
-      <c r="E8" s="256"/>
-      <c r="F8" s="256"/>
-      <c r="G8" s="256"/>
-      <c r="H8" s="257"/>
+      <c r="E8" s="236"/>
+      <c r="F8" s="236"/>
+      <c r="G8" s="236"/>
+      <c r="H8" s="237"/>
     </row>
     <row r="9" spans="2:14">
-      <c r="B9" s="242" t="s">
+      <c r="B9" s="233" t="s">
         <v>43</v>
       </c>
-      <c r="C9" s="243"/>
-      <c r="D9" s="261" t="s">
+      <c r="C9" s="234"/>
+      <c r="D9" s="238" t="s">
         <v>224</v>
       </c>
-      <c r="E9" s="262"/>
-      <c r="F9" s="262"/>
-      <c r="G9" s="262"/>
-      <c r="H9" s="263"/>
-    </row>
-    <row r="10" spans="2:14" ht="13.5" thickBot="1">
+      <c r="E9" s="239"/>
+      <c r="F9" s="239"/>
+      <c r="G9" s="239"/>
+      <c r="H9" s="240"/>
+    </row>
+    <row r="10" spans="2:14" ht="14.25" thickBot="1">
       <c r="B10" s="244" t="s">
         <v>49</v>
       </c>
       <c r="C10" s="245"/>
-      <c r="D10" s="264" t="s">
-        <v>285</v>
-      </c>
-      <c r="E10" s="265"/>
-      <c r="F10" s="265"/>
-      <c r="G10" s="265"/>
-      <c r="H10" s="266"/>
-    </row>
-    <row r="11" spans="2:14" ht="13.5" thickBot="1"/>
-    <row r="12" spans="2:14" ht="13.5" thickBot="1">
+      <c r="D10" s="241" t="s">
+        <v>259</v>
+      </c>
+      <c r="E10" s="242"/>
+      <c r="F10" s="242"/>
+      <c r="G10" s="242"/>
+      <c r="H10" s="243"/>
+    </row>
+    <row r="11" spans="2:14" ht="14.25" thickBot="1"/>
+    <row r="12" spans="2:14" ht="14.25" thickBot="1">
       <c r="B12" s="147" t="s">
         <v>39</v>
       </c>
@@ -10133,7 +8326,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="13" spans="2:14" ht="13.5" thickTop="1">
+    <row r="13" spans="2:14" ht="14.25" thickTop="1">
       <c r="B13" s="106">
         <v>1</v>
       </c>
@@ -10986,7 +9179,7 @@
         <v/>
       </c>
     </row>
-    <row r="37" spans="2:14" ht="13.5" thickBot="1">
+    <row r="37" spans="2:14" ht="14.25" thickBot="1">
       <c r="B37" s="97">
         <v>25</v>
       </c>
@@ -11027,22 +9220,22 @@
     <protectedRange sqref="D2:H3 D9:H10 C13:E37" name="編集許可"/>
   </protectedRanges>
   <mergeCells count="16">
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="D2:H2"/>
+    <mergeCell ref="D4:H4"/>
+    <mergeCell ref="D6:H6"/>
+    <mergeCell ref="D7:H7"/>
+    <mergeCell ref="D3:H3"/>
     <mergeCell ref="B9:C9"/>
     <mergeCell ref="D8:H8"/>
     <mergeCell ref="D9:H9"/>
     <mergeCell ref="D10:H10"/>
     <mergeCell ref="B10:C10"/>
     <mergeCell ref="B8:C8"/>
-    <mergeCell ref="D2:H2"/>
-    <mergeCell ref="D4:H4"/>
-    <mergeCell ref="D6:H6"/>
-    <mergeCell ref="D7:H7"/>
-    <mergeCell ref="D3:H3"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B7:C7"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
   <conditionalFormatting sqref="C13:C37">
@@ -11088,21 +9281,21 @@
     <tabColor rgb="FFCCFFCC"/>
   </sheetPr>
   <dimension ref="B2:R59"/>
-  <sheetFormatPr defaultRowHeight="13"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="2" max="2" width="3.7265625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.08984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="3.75" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="13" customWidth="1"/>
-    <col min="5" max="5" width="36.453125" customWidth="1"/>
-    <col min="6" max="6" width="52.7265625" customWidth="1"/>
-    <col min="7" max="7" width="7.08984375" bestFit="1" customWidth="1"/>
-    <col min="8" max="15" width="3.90625" customWidth="1"/>
-    <col min="16" max="16" width="9.90625" customWidth="1"/>
-    <col min="17" max="17" width="44.6328125" customWidth="1"/>
-    <col min="18" max="18" width="73.6328125" customWidth="1"/>
+    <col min="5" max="5" width="36.5" customWidth="1"/>
+    <col min="6" max="6" width="52.75" customWidth="1"/>
+    <col min="7" max="7" width="7.125" bestFit="1" customWidth="1"/>
+    <col min="8" max="15" width="3.875" customWidth="1"/>
+    <col min="16" max="16" width="9.875" customWidth="1"/>
+    <col min="17" max="17" width="44.625" customWidth="1"/>
+    <col min="18" max="18" width="73.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:18" ht="13.5" thickBot="1">
+    <row r="2" spans="2:18" ht="14.25" thickBot="1">
       <c r="B2" t="s">
         <v>210</v>
       </c>
@@ -11110,7 +9303,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="3" spans="2:18" ht="13.5" thickBot="1">
+    <row r="3" spans="2:18" ht="14.25" thickBot="1">
       <c r="B3" s="147" t="s">
         <v>39</v>
       </c>
@@ -11148,7 +9341,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="4" spans="2:18" ht="13.5" hidden="1" thickTop="1">
+    <row r="4" spans="2:18" ht="14.25" hidden="1" thickTop="1">
       <c r="B4" s="178">
         <v>0</v>
       </c>
@@ -11176,7 +9369,7 @@
       </c>
       <c r="R4" s="143"/>
     </row>
-    <row r="5" spans="2:18" ht="13.5" thickTop="1">
+    <row r="5" spans="2:18" ht="14.25" thickTop="1">
       <c r="B5" s="181">
         <v>1</v>
       </c>
@@ -11704,7 +9897,7 @@
       <c r="Q28" s="151"/>
       <c r="R28" s="118"/>
     </row>
-    <row r="29" spans="2:18" ht="13.5" thickBot="1">
+    <row r="29" spans="2:18" ht="14.25" thickBot="1">
       <c r="B29" s="182">
         <v>25</v>
       </c>
@@ -11726,7 +9919,7 @@
       <c r="Q29" s="149"/>
       <c r="R29" s="120"/>
     </row>
-    <row r="32" spans="2:18" ht="13.5" thickBot="1">
+    <row r="32" spans="2:18" ht="14.25" thickBot="1">
       <c r="B32" t="s">
         <v>211</v>
       </c>
@@ -11734,7 +9927,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="33" spans="2:18" ht="13.5" thickBot="1">
+    <row r="33" spans="2:18" ht="14.25" thickBot="1">
       <c r="B33" s="147" t="s">
         <v>39</v>
       </c>
@@ -11766,7 +9959,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="34" spans="2:18" ht="13.5" hidden="1" thickTop="1">
+    <row r="34" spans="2:18" ht="14.25" hidden="1" thickTop="1">
       <c r="B34" s="178">
         <v>0</v>
       </c>
@@ -11792,7 +9985,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="35" spans="2:18" ht="13.5" thickTop="1">
+    <row r="35" spans="2:18" ht="14.25" thickTop="1">
       <c r="B35" s="181">
         <v>1</v>
       </c>
@@ -12320,7 +10513,7 @@
       <c r="Q58" s="151"/>
       <c r="R58" s="183"/>
     </row>
-    <row r="59" spans="2:18" ht="13.5" thickBot="1">
+    <row r="59" spans="2:18" ht="14.25" thickBot="1">
       <c r="B59" s="182">
         <v>25</v>
       </c>
@@ -12371,29 +10564,29 @@
     <tabColor rgb="FFCCFFCC"/>
   </sheetPr>
   <dimension ref="B1:U103"/>
-  <sheetFormatPr defaultRowHeight="13"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="2" max="2" width="28.36328125" customWidth="1"/>
-    <col min="3" max="3" width="15.90625" customWidth="1"/>
-    <col min="5" max="5" width="12.36328125" customWidth="1"/>
-    <col min="6" max="6" width="19.7265625" customWidth="1"/>
-    <col min="7" max="7" width="12.36328125" customWidth="1"/>
-    <col min="8" max="8" width="29.26953125" customWidth="1"/>
-    <col min="9" max="9" width="12.36328125" customWidth="1"/>
-    <col min="10" max="10" width="26.7265625" customWidth="1"/>
-    <col min="11" max="11" width="12.36328125" customWidth="1"/>
-    <col min="12" max="12" width="16.08984375" customWidth="1"/>
-    <col min="14" max="14" width="30.08984375" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="57.08984375" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="28.375" customWidth="1"/>
+    <col min="3" max="3" width="15.875" customWidth="1"/>
+    <col min="5" max="5" width="12.375" customWidth="1"/>
+    <col min="6" max="6" width="19.75" customWidth="1"/>
+    <col min="7" max="7" width="12.375" customWidth="1"/>
+    <col min="8" max="8" width="29.25" customWidth="1"/>
+    <col min="9" max="9" width="12.375" customWidth="1"/>
+    <col min="10" max="10" width="26.75" customWidth="1"/>
+    <col min="11" max="11" width="12.375" customWidth="1"/>
+    <col min="12" max="12" width="16.125" customWidth="1"/>
+    <col min="14" max="14" width="30.125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="57.125" hidden="1" customWidth="1"/>
     <col min="21" max="21" width="13" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:21" ht="13.5" thickBot="1">
+    <row r="1" spans="2:21" ht="14.25" thickBot="1">
       <c r="C1" s="90" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="2" spans="2:21" ht="13.5" thickBot="1">
+    <row r="2" spans="2:21" ht="14.25" thickBot="1">
       <c r="B2" s="98" t="s">
         <v>63</v>
       </c>
@@ -12437,7 +10630,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="3" spans="2:21" ht="14" hidden="1" thickTop="1" thickBot="1">
+    <row r="3" spans="2:21" ht="15" hidden="1" thickTop="1" thickBot="1">
       <c r="B3" s="25"/>
       <c r="C3" s="51" t="s">
         <v>113</v>
@@ -12458,12 +10651,12 @@
         <v>103</v>
       </c>
     </row>
-    <row r="4" spans="2:21" ht="13.5" thickTop="1">
+    <row r="4" spans="2:21" ht="14.25" thickTop="1">
       <c r="B4" s="25" t="s">
-        <v>261</v>
+        <v>248</v>
       </c>
       <c r="C4" s="51" t="s">
-        <v>264</v>
+        <v>250</v>
       </c>
       <c r="D4" s="114">
         <v>0</v>
@@ -12478,7 +10671,7 @@
         <v>131</v>
       </c>
       <c r="H4" s="116" t="s">
-        <v>281</v>
+        <v>258</v>
       </c>
       <c r="I4" s="115" t="s">
         <v>131</v>
@@ -12517,7 +10710,7 @@
       <c r="G5" s="25"/>
       <c r="H5" s="118"/>
       <c r="I5" s="25"/>
-      <c r="J5" s="199"/>
+      <c r="J5" s="198"/>
       <c r="K5" s="25"/>
       <c r="L5" s="118"/>
       <c r="M5" s="47" t="e">
@@ -12541,13 +10734,13 @@
       <c r="C6" s="107"/>
       <c r="D6" s="121"/>
       <c r="E6" s="109"/>
-      <c r="F6" s="199"/>
+      <c r="F6" s="198"/>
       <c r="G6" s="109"/>
-      <c r="H6" s="216"/>
+      <c r="H6" s="214"/>
       <c r="I6" s="109"/>
-      <c r="J6" s="199"/>
+      <c r="J6" s="198"/>
       <c r="K6" s="109"/>
-      <c r="L6" s="199"/>
+      <c r="L6" s="198"/>
       <c r="M6" s="47" t="e">
         <f t="shared" ca="1" si="1"/>
         <v>#N/A</v>
@@ -12726,7 +10919,7 @@
       </c>
       <c r="U12" s="31"/>
     </row>
-    <row r="13" spans="2:21" ht="13.5" thickBot="1">
+    <row r="13" spans="2:21" ht="14.25" thickBot="1">
       <c r="B13" s="25"/>
       <c r="C13" s="24"/>
       <c r="D13" s="117"/>
@@ -14977,7 +13170,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="103" spans="2:15" ht="13.5" thickBot="1">
+    <row r="103" spans="2:15" ht="14.25" thickBot="1">
       <c r="B103" s="53"/>
       <c r="C103" s="54"/>
       <c r="D103" s="119"/>
@@ -15050,18 +13243,18 @@
     <tabColor rgb="FFCCECFF"/>
   </sheetPr>
   <dimension ref="A1:AW199"/>
-  <sheetFormatPr defaultRowHeight="13"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
-    <col min="2" max="2" width="16.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.75" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="3" bestFit="1" customWidth="1"/>
     <col min="4" max="35" width="3" customWidth="1"/>
-    <col min="36" max="36" width="36.36328125" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="4.08984375" customWidth="1"/>
+    <col min="36" max="36" width="36.375" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="4.125" customWidth="1"/>
     <col min="38" max="42" width="9" hidden="1" customWidth="1"/>
-    <col min="43" max="43" width="20.6328125" hidden="1" customWidth="1"/>
-    <col min="44" max="47" width="41.08984375" customWidth="1"/>
-    <col min="48" max="48" width="23.6328125" customWidth="1"/>
+    <col min="43" max="43" width="20.625" hidden="1" customWidth="1"/>
+    <col min="44" max="47" width="41.125" customWidth="1"/>
+    <col min="48" max="48" width="23.625" customWidth="1"/>
     <col min="49" max="49" width="29" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -15077,7 +13270,7 @@
       <c r="B2" s="127" t="s">
         <v>128</v>
       </c>
-      <c r="C2" s="267" t="s">
+      <c r="C2" s="260" t="s">
         <v>89</v>
       </c>
       <c r="D2" s="58">
@@ -15176,16 +13369,16 @@
       <c r="AI2" s="58">
         <v>0</v>
       </c>
-      <c r="AJ2" s="269" t="s">
+      <c r="AJ2" s="262" t="s">
         <v>162</v>
       </c>
     </row>
     <row r="3" spans="1:49" ht="213" customHeight="1" thickBot="1">
-      <c r="B3" s="221" t="str">
+      <c r="B3" s="216" t="str">
         <f>IF(OR(IF(COUNTIF(D6:AC69,"0")&lt;&gt;0,TRUE,FALSE),IF(COUNTIF(D6:AC69,"1")&lt;&gt;0,TRUE,FALSE)),"Search Table","Index Table")</f>
         <v>Index Table</v>
       </c>
-      <c r="C3" s="268"/>
+      <c r="C3" s="261"/>
       <c r="D3" s="129" t="s">
         <v>66</v>
       </c>
@@ -15270,24 +13463,24 @@
       <c r="AE3" s="130" t="s">
         <v>67</v>
       </c>
-      <c r="AF3" s="275" t="s">
-        <v>290</v>
-      </c>
-      <c r="AG3" s="276"/>
-      <c r="AH3" s="275" t="s">
-        <v>280</v>
-      </c>
-      <c r="AI3" s="276"/>
-      <c r="AJ3" s="270"/>
+      <c r="AF3" s="268" t="s">
+        <v>262</v>
+      </c>
+      <c r="AG3" s="269"/>
+      <c r="AH3" s="268" t="s">
+        <v>257</v>
+      </c>
+      <c r="AI3" s="269"/>
+      <c r="AJ3" s="263"/>
       <c r="AR3" s="91" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="4" spans="1:49" ht="13.5" thickBot="1">
-      <c r="A4" s="271" t="s">
+    <row r="4" spans="1:49" ht="14.25" thickBot="1">
+      <c r="A4" s="264" t="s">
         <v>68</v>
       </c>
-      <c r="B4" s="272"/>
+      <c r="B4" s="265"/>
       <c r="C4" s="139"/>
       <c r="D4" s="139"/>
       <c r="E4" s="139"/>
@@ -15331,9 +13524,9 @@
       <c r="AV4" s="80"/>
       <c r="AW4" s="81"/>
     </row>
-    <row r="5" spans="1:49" ht="13.5" thickBot="1">
-      <c r="A5" s="273"/>
-      <c r="B5" s="274"/>
+    <row r="5" spans="1:49" ht="14.25" thickBot="1">
+      <c r="A5" s="266"/>
+      <c r="B5" s="267"/>
       <c r="C5" s="140"/>
       <c r="D5" s="140"/>
       <c r="E5" s="140"/>
@@ -15628,7 +13821,7 @@
         <v>1</v>
       </c>
       <c r="AJ7" s="24" t="s">
-        <v>263</v>
+        <v>249</v>
       </c>
       <c r="AL7" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -16848,7 +15041,7 @@
         <v>ALERT_VOM_IGN_ON</v>
       </c>
     </row>
-    <row r="17" spans="2:49" ht="13.5" thickBot="1">
+    <row r="17" spans="2:49" ht="14.25" thickBot="1">
       <c r="B17" s="136"/>
       <c r="C17" s="47">
         <f t="shared" si="2"/>
@@ -23228,7 +21421,7 @@
         <v/>
       </c>
     </row>
-    <row r="70" spans="1:46" ht="13.5" thickBot="1">
+    <row r="70" spans="1:46" ht="14.25" thickBot="1">
       <c r="A70" s="56" t="s">
         <v>69</v>
       </c>
@@ -43855,74 +42048,47 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <sheetPr codeName="Sheet5"/>
-  <dimension ref="B2:AO120"/>
-  <sheetFormatPr defaultRowHeight="13"/>
+  <dimension ref="B4:AN45"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="2" max="2" width="35.36328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="10" width="3.36328125" customWidth="1"/>
-    <col min="11" max="11" width="20.7265625" customWidth="1"/>
-    <col min="12" max="12" width="23.36328125" customWidth="1"/>
-    <col min="13" max="13" width="17" customWidth="1"/>
-    <col min="14" max="14" width="20.90625" customWidth="1"/>
-    <col min="15" max="15" width="10.90625" customWidth="1"/>
-    <col min="16" max="16" width="13.36328125" customWidth="1"/>
-    <col min="17" max="18" width="10.90625" customWidth="1"/>
+    <col min="2" max="2" width="35.375" bestFit="1" customWidth="1"/>
+    <col min="3" max="10" width="3.375" customWidth="1"/>
+    <col min="11" max="11" width="20.75" customWidth="1"/>
+    <col min="12" max="12" width="17" customWidth="1"/>
+    <col min="13" max="13" width="20.875" customWidth="1"/>
+    <col min="14" max="14" width="10.875" customWidth="1"/>
+    <col min="15" max="15" width="13.375" customWidth="1"/>
+    <col min="16" max="17" width="10.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:41">
-      <c r="U2" s="200" t="s">
-        <v>228</v>
-      </c>
-      <c r="V2" s="200"/>
-      <c r="W2" s="200"/>
-      <c r="X2" s="200"/>
-      <c r="Y2" s="200"/>
-      <c r="Z2" s="200"/>
-      <c r="AA2" s="200"/>
-      <c r="AB2" s="200"/>
-      <c r="AC2" s="200"/>
-      <c r="AD2" s="200"/>
-      <c r="AE2" s="200"/>
-      <c r="AF2" s="200"/>
-      <c r="AG2" s="200"/>
-      <c r="AH2" s="200"/>
-      <c r="AI2" s="200"/>
-      <c r="AJ2" s="200"/>
-      <c r="AK2" s="200"/>
-      <c r="AL2" s="200"/>
-      <c r="AM2" s="200"/>
-      <c r="AN2" s="200"/>
-      <c r="AO2" s="200"/>
-    </row>
-    <row r="4" spans="2:41" ht="14.5" thickBot="1">
+    <row r="4" spans="2:17" ht="15" thickBot="1">
       <c r="B4" s="26" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="5" spans="2:41" ht="14.5" thickBot="1">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="5" spans="2:17" ht="15" thickBot="1">
       <c r="B5" s="95" t="s">
         <v>165</v>
       </c>
-      <c r="C5" s="281" t="s">
+      <c r="C5" s="274" t="s">
         <v>222</v>
       </c>
-      <c r="D5" s="282"/>
-      <c r="E5" s="282"/>
-      <c r="F5" s="282"/>
-      <c r="G5" s="282"/>
-      <c r="H5" s="282"/>
-      <c r="I5" s="282"/>
-      <c r="J5" s="283"/>
+      <c r="D5" s="275"/>
+      <c r="E5" s="275"/>
+      <c r="F5" s="275"/>
+      <c r="G5" s="275"/>
+      <c r="H5" s="275"/>
+      <c r="I5" s="275"/>
+      <c r="J5" s="276"/>
       <c r="K5" s="174"/>
       <c r="L5" s="174"/>
-      <c r="M5" s="174"/>
-      <c r="N5" s="177"/>
+      <c r="M5" s="177"/>
+      <c r="N5" s="175"/>
       <c r="O5" s="175"/>
       <c r="P5" s="175"/>
-      <c r="Q5" s="175"/>
-      <c r="R5" s="176"/>
-    </row>
-    <row r="6" spans="2:41">
+      <c r="Q5" s="176"/>
+    </row>
+    <row r="6" spans="2:17">
       <c r="B6" s="70"/>
       <c r="C6" s="34" t="s">
         <v>169</v>
@@ -43935,54 +42101,52 @@
       <c r="I6" s="34"/>
       <c r="J6" s="34"/>
       <c r="K6" s="34"/>
-      <c r="L6" s="34"/>
-      <c r="M6" s="35"/>
-      <c r="N6" s="30" t="s">
+      <c r="L6" s="35"/>
+      <c r="M6" s="30" t="s">
         <v>157</v>
       </c>
-      <c r="O6" s="43" t="s">
+      <c r="N6" s="43" t="s">
         <v>21</v>
       </c>
+      <c r="O6" s="44"/>
       <c r="P6" s="44"/>
-      <c r="Q6" s="44"/>
-      <c r="R6" s="45"/>
-    </row>
-    <row r="7" spans="2:41">
+      <c r="Q6" s="45"/>
+    </row>
+    <row r="7" spans="2:17">
       <c r="B7" s="71" t="s">
         <v>22</v>
       </c>
-      <c r="C7" s="277" t="s">
+      <c r="C7" s="270" t="s">
         <v>189</v>
       </c>
-      <c r="D7" s="278"/>
-      <c r="E7" s="278"/>
-      <c r="F7" s="278"/>
-      <c r="G7" s="278"/>
-      <c r="H7" s="278"/>
-      <c r="I7" s="278"/>
-      <c r="J7" s="279"/>
+      <c r="D7" s="271"/>
+      <c r="E7" s="271"/>
+      <c r="F7" s="271"/>
+      <c r="G7" s="271"/>
+      <c r="H7" s="271"/>
+      <c r="I7" s="271"/>
+      <c r="J7" s="272"/>
       <c r="K7" s="38" t="s">
         <v>23</v>
       </c>
-      <c r="L7" s="198"/>
-      <c r="M7" s="75"/>
-      <c r="N7" s="31" t="s">
-        <v>240</v>
-      </c>
-      <c r="O7" s="202" t="s">
+      <c r="L7" s="75"/>
+      <c r="M7" s="31" t="s">
+        <v>236</v>
+      </c>
+      <c r="N7" s="201" t="s">
         <v>24</v>
       </c>
-      <c r="P7" s="206" t="s">
+      <c r="O7" s="277" t="s">
         <v>25</v>
       </c>
-      <c r="Q7" s="206" t="s">
+      <c r="P7" s="205" t="s">
         <v>26</v>
       </c>
-      <c r="R7" s="143" t="s">
+      <c r="Q7" s="143" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="8" spans="2:41">
+    <row r="8" spans="2:17">
       <c r="B8" s="71" t="s">
         <v>38</v>
       </c>
@@ -44016,47 +42180,41 @@
       <c r="L8" s="142" t="s">
         <v>216</v>
       </c>
-      <c r="M8" s="142" t="s">
-        <v>216</v>
-      </c>
-      <c r="N8" s="31" t="s">
+      <c r="M8" s="31" t="s">
         <v>218</v>
       </c>
-      <c r="O8" s="203"/>
-      <c r="P8" s="207"/>
-      <c r="Q8" s="207"/>
-      <c r="R8" s="143"/>
-    </row>
-    <row r="9" spans="2:41" ht="26">
+      <c r="N8" s="202"/>
+      <c r="O8" s="278"/>
+      <c r="P8" s="206"/>
+      <c r="Q8" s="143"/>
+    </row>
+    <row r="9" spans="2:17" ht="27">
       <c r="B9" s="72" t="s">
         <v>28</v>
       </c>
-      <c r="C9" s="280" t="s">
+      <c r="C9" s="273" t="s">
         <v>171</v>
       </c>
-      <c r="D9" s="278"/>
-      <c r="E9" s="278"/>
-      <c r="F9" s="278"/>
-      <c r="G9" s="278"/>
-      <c r="H9" s="278"/>
-      <c r="I9" s="278"/>
-      <c r="J9" s="279"/>
+      <c r="D9" s="271"/>
+      <c r="E9" s="271"/>
+      <c r="F9" s="271"/>
+      <c r="G9" s="271"/>
+      <c r="H9" s="271"/>
+      <c r="I9" s="271"/>
+      <c r="J9" s="272"/>
       <c r="K9" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="L9" s="1" t="s">
         <v>235</v>
       </c>
-      <c r="L9" s="1" t="s">
-        <v>232</v>
-      </c>
-      <c r="M9" s="1" t="s">
-        <v>239</v>
-      </c>
-      <c r="N9" s="32"/>
-      <c r="O9" s="203"/>
-      <c r="P9" s="207"/>
-      <c r="Q9" s="207"/>
-      <c r="R9" s="143"/>
-    </row>
-    <row r="10" spans="2:41" ht="131">
+      <c r="M9" s="32"/>
+      <c r="N9" s="202"/>
+      <c r="O9" s="278"/>
+      <c r="P9" s="206"/>
+      <c r="Q9" s="143"/>
+    </row>
+    <row r="10" spans="2:17" ht="136.5">
       <c r="B10" s="71" t="s">
         <v>29</v>
       </c>
@@ -44085,23 +42243,20 @@
         <v>178</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>247</v>
+        <v>237</v>
       </c>
       <c r="L10" s="28" t="s">
-        <v>279</v>
-      </c>
-      <c r="M10" s="28" t="s">
-        <v>280</v>
-      </c>
-      <c r="N10" s="31" t="s">
+        <v>257</v>
+      </c>
+      <c r="M10" s="31" t="s">
         <v>30</v>
       </c>
-      <c r="O10" s="203"/>
-      <c r="P10" s="207"/>
-      <c r="Q10" s="207"/>
-      <c r="R10" s="143"/>
-    </row>
-    <row r="11" spans="2:41" ht="64.5" customHeight="1" thickBot="1">
+      <c r="N10" s="202"/>
+      <c r="O10" s="278"/>
+      <c r="P10" s="206"/>
+      <c r="Q10" s="143"/>
+    </row>
+    <row r="11" spans="2:17" ht="64.5" customHeight="1" thickBot="1">
       <c r="B11" s="73" t="s">
         <v>31</v>
       </c>
@@ -44130,29 +42285,24 @@
         <v>180</v>
       </c>
       <c r="K11" s="27" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="L11" s="29" t="s">
-        <v>244</v>
-      </c>
-      <c r="M11" s="29" t="s">
-        <v>236</v>
-      </c>
-      <c r="N11" s="33" t="s">
-        <v>271</v>
-      </c>
-      <c r="O11" s="204"/>
-      <c r="P11" s="208" t="s">
-        <v>287</v>
-      </c>
-      <c r="Q11" s="212" t="s">
-        <v>267</v>
-      </c>
-      <c r="R11" s="144"/>
-    </row>
-    <row r="12" spans="2:41" ht="13.5" thickTop="1">
+        <v>232</v>
+      </c>
+      <c r="M11" s="33" t="s">
+        <v>269</v>
+      </c>
+      <c r="N11" s="203"/>
+      <c r="O11" s="279"/>
+      <c r="P11" s="210" t="s">
+        <v>252</v>
+      </c>
+      <c r="Q11" s="144"/>
+    </row>
+    <row r="12" spans="2:17" ht="14.25" thickTop="1">
       <c r="B12" s="74" t="s">
-        <v>231</v>
+        <v>270</v>
       </c>
       <c r="C12" s="172" t="s">
         <v>179</v>
@@ -44179,29 +42329,24 @@
         <v>179</v>
       </c>
       <c r="K12" s="39" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="L12" s="40" t="s">
         <v>33</v>
       </c>
-      <c r="M12" s="40" t="s">
-        <v>33</v>
-      </c>
-      <c r="N12" s="41" t="s">
+      <c r="M12" s="41" t="s">
         <v>225</v>
       </c>
-      <c r="O12" s="205"/>
-      <c r="P12" s="209" t="s">
-        <v>253</v>
-      </c>
-      <c r="Q12" s="209" t="s">
-        <v>256</v>
-      </c>
-      <c r="R12" s="145"/>
-    </row>
-    <row r="13" spans="2:41">
+      <c r="N12" s="204"/>
+      <c r="O12" s="280"/>
+      <c r="P12" s="207" t="s">
+        <v>244</v>
+      </c>
+      <c r="Q12" s="145"/>
+    </row>
+    <row r="13" spans="2:17">
       <c r="B13" s="74" t="s">
-        <v>245</v>
+        <v>271</v>
       </c>
       <c r="C13" s="173" t="s">
         <v>179</v>
@@ -44228,29 +42373,24 @@
         <v>179</v>
       </c>
       <c r="K13" s="36" t="s">
-        <v>237</v>
-      </c>
-      <c r="L13" s="40" t="s">
-        <v>33</v>
-      </c>
-      <c r="M13" s="37" t="s">
+        <v>233</v>
+      </c>
+      <c r="L13" s="37" t="s">
         <v>35</v>
       </c>
-      <c r="N13" s="42" t="s">
-        <v>265</v>
-      </c>
-      <c r="O13" s="173"/>
-      <c r="P13" s="210" t="s">
+      <c r="M13" s="42" t="s">
+        <v>251</v>
+      </c>
+      <c r="N13" s="173"/>
+      <c r="O13" s="281"/>
+      <c r="P13" s="208" t="s">
         <v>253</v>
       </c>
-      <c r="Q13" s="210" t="s">
-        <v>268</v>
-      </c>
-      <c r="R13" s="146"/>
-    </row>
-    <row r="14" spans="2:41">
+      <c r="Q13" s="146"/>
+    </row>
+    <row r="14" spans="2:17">
       <c r="B14" s="74" t="s">
-        <v>231</v>
+        <v>270</v>
       </c>
       <c r="C14" s="173" t="s">
         <v>179</v>
@@ -44277,29 +42417,24 @@
         <v>179</v>
       </c>
       <c r="K14" s="36" t="s">
-        <v>238</v>
-      </c>
-      <c r="L14" s="40" t="s">
-        <v>33</v>
-      </c>
-      <c r="M14" s="37" t="s">
+        <v>234</v>
+      </c>
+      <c r="L14" s="37" t="s">
         <v>36</v>
       </c>
-      <c r="N14" s="42" t="s">
+      <c r="M14" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="O14" s="173"/>
-      <c r="P14" s="210" t="s">
-        <v>253</v>
-      </c>
-      <c r="Q14" s="210" t="s">
-        <v>255</v>
-      </c>
-      <c r="R14" s="146"/>
-    </row>
-    <row r="15" spans="2:41">
+      <c r="N14" s="173"/>
+      <c r="O14" s="281"/>
+      <c r="P14" s="208" t="s">
+        <v>243</v>
+      </c>
+      <c r="Q14" s="146"/>
+    </row>
+    <row r="15" spans="2:17">
       <c r="B15" s="74" t="s">
-        <v>231</v>
+        <v>270</v>
       </c>
       <c r="C15" s="173" t="s">
         <v>179</v>
@@ -44326,78 +42461,68 @@
         <v>179</v>
       </c>
       <c r="K15" s="197" t="s">
+        <v>234</v>
+      </c>
+      <c r="L15" s="37" t="s">
+        <v>37</v>
+      </c>
+      <c r="M15" s="42" t="s">
+        <v>34</v>
+      </c>
+      <c r="N15" s="173"/>
+      <c r="O15" s="281"/>
+      <c r="P15" s="208" t="s">
+        <v>246</v>
+      </c>
+      <c r="Q15" s="146"/>
+    </row>
+    <row r="16" spans="2:17">
+      <c r="B16" s="22" t="s">
         <v>238</v>
       </c>
-      <c r="L15" s="40" t="s">
-        <v>33</v>
-      </c>
-      <c r="M15" s="37" t="s">
-        <v>37</v>
-      </c>
-      <c r="N15" s="42" t="s">
+      <c r="C16" s="173" t="s">
+        <v>179</v>
+      </c>
+      <c r="D16" s="173" t="s">
+        <v>179</v>
+      </c>
+      <c r="E16" s="173" t="s">
+        <v>179</v>
+      </c>
+      <c r="F16" s="173" t="s">
+        <v>179</v>
+      </c>
+      <c r="G16" s="173" t="s">
+        <v>179</v>
+      </c>
+      <c r="H16" s="173" t="s">
+        <v>179</v>
+      </c>
+      <c r="I16" s="173" t="s">
+        <v>179</v>
+      </c>
+      <c r="J16" s="173" t="s">
+        <v>179</v>
+      </c>
+      <c r="K16" s="61" t="s">
+        <v>35</v>
+      </c>
+      <c r="L16" s="197" t="s">
+        <v>226</v>
+      </c>
+      <c r="M16" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="O15" s="173"/>
-      <c r="P15" s="210" t="s">
-        <v>253</v>
-      </c>
-      <c r="Q15" s="210" t="s">
-        <v>259</v>
-      </c>
-      <c r="R15" s="146"/>
-    </row>
-    <row r="16" spans="2:41">
-      <c r="B16" s="74" t="s">
-        <v>246</v>
-      </c>
-      <c r="C16" s="172" t="s">
-        <v>179</v>
-      </c>
-      <c r="D16" s="172" t="s">
-        <v>179</v>
-      </c>
-      <c r="E16" s="172" t="s">
-        <v>179</v>
-      </c>
-      <c r="F16" s="172" t="s">
-        <v>179</v>
-      </c>
-      <c r="G16" s="172" t="s">
-        <v>179</v>
-      </c>
-      <c r="H16" s="172" t="s">
-        <v>179</v>
-      </c>
-      <c r="I16" s="172" t="s">
-        <v>179</v>
-      </c>
-      <c r="J16" s="172" t="s">
-        <v>179</v>
-      </c>
-      <c r="K16" s="39" t="s">
-        <v>237</v>
-      </c>
-      <c r="L16" s="40" t="s">
-        <v>241</v>
-      </c>
-      <c r="M16" s="40" t="s">
-        <v>33</v>
-      </c>
-      <c r="N16" s="41" t="s">
-        <v>272</v>
-      </c>
-      <c r="O16" s="205"/>
-      <c r="P16" s="225" t="s">
-        <v>282</v>
-      </c>
-      <c r="Q16" s="209" t="s">
-        <v>256</v>
-      </c>
-      <c r="R16" s="145"/>
-    </row>
-    <row r="17" spans="2:18">
-      <c r="B17" s="74" t="s">
-        <v>262</v>
+      <c r="N16" s="173"/>
+      <c r="O16" s="281"/>
+      <c r="P16" s="208" t="s">
+        <v>242</v>
+      </c>
+      <c r="Q16" s="146"/>
+    </row>
+    <row r="17" spans="2:17">
+      <c r="B17" s="22" t="s">
+        <v>239</v>
       </c>
       <c r="C17" s="173" t="s">
         <v>179</v>
@@ -44424,29 +42549,24 @@
         <v>179</v>
       </c>
       <c r="K17" s="61" t="s">
-        <v>237</v>
-      </c>
-      <c r="L17" s="218" t="s">
-        <v>241</v>
-      </c>
-      <c r="M17" s="219" t="s">
-        <v>35</v>
-      </c>
-      <c r="N17" s="220" t="s">
-        <v>273</v>
-      </c>
-      <c r="O17" s="173"/>
-      <c r="P17" s="226" t="s">
-        <v>282</v>
-      </c>
-      <c r="Q17" s="210" t="s">
-        <v>269</v>
-      </c>
-      <c r="R17" s="146"/>
-    </row>
-    <row r="18" spans="2:18">
-      <c r="B18" s="74" t="s">
-        <v>246</v>
+        <v>36</v>
+      </c>
+      <c r="L17" s="197" t="s">
+        <v>226</v>
+      </c>
+      <c r="M17" s="42" t="s">
+        <v>34</v>
+      </c>
+      <c r="N17" s="173"/>
+      <c r="O17" s="281"/>
+      <c r="P17" s="208" t="s">
+        <v>245</v>
+      </c>
+      <c r="Q17" s="146"/>
+    </row>
+    <row r="18" spans="2:17">
+      <c r="B18" s="22" t="s">
+        <v>240</v>
       </c>
       <c r="C18" s="173" t="s">
         <v>179</v>
@@ -44472,709 +42592,218 @@
       <c r="J18" s="173" t="s">
         <v>179</v>
       </c>
-      <c r="K18" s="197" t="s">
-        <v>238</v>
-      </c>
-      <c r="L18" s="40" t="s">
+      <c r="K18" s="61" t="s">
+        <v>37</v>
+      </c>
+      <c r="L18" s="197" t="s">
+        <v>226</v>
+      </c>
+      <c r="M18" s="42" t="s">
+        <v>34</v>
+      </c>
+      <c r="N18" s="173"/>
+      <c r="O18" s="281"/>
+      <c r="P18" s="208" t="s">
+        <v>242</v>
+      </c>
+      <c r="Q18" s="146"/>
+    </row>
+    <row r="19" spans="2:17" ht="14.25" thickBot="1">
+      <c r="B19" s="212" t="s">
         <v>241</v>
       </c>
-      <c r="M18" s="37" t="s">
-        <v>36</v>
-      </c>
-      <c r="N18" s="41" t="s">
-        <v>274</v>
-      </c>
-      <c r="O18" s="173"/>
-      <c r="P18" s="226" t="s">
-        <v>282</v>
-      </c>
-      <c r="Q18" s="210" t="s">
-        <v>253</v>
-      </c>
-      <c r="R18" s="146"/>
-    </row>
-    <row r="19" spans="2:18">
-      <c r="B19" s="74" t="s">
-        <v>246</v>
-      </c>
-      <c r="C19" s="173" t="s">
+      <c r="C19" s="213" t="s">
         <v>179</v>
       </c>
-      <c r="D19" s="173" t="s">
+      <c r="D19" s="213" t="s">
         <v>179</v>
       </c>
-      <c r="E19" s="173" t="s">
+      <c r="E19" s="213" t="s">
         <v>179</v>
       </c>
-      <c r="F19" s="173" t="s">
+      <c r="F19" s="213" t="s">
         <v>179</v>
       </c>
-      <c r="G19" s="173" t="s">
+      <c r="G19" s="213" t="s">
         <v>179</v>
       </c>
-      <c r="H19" s="173" t="s">
+      <c r="H19" s="213" t="s">
         <v>179</v>
       </c>
-      <c r="I19" s="173" t="s">
+      <c r="I19" s="213" t="s">
         <v>179</v>
       </c>
-      <c r="J19" s="173" t="s">
+      <c r="J19" s="213" t="s">
         <v>179</v>
       </c>
-      <c r="K19" s="197" t="s">
-        <v>238</v>
-      </c>
-      <c r="L19" s="40" t="s">
-        <v>241</v>
-      </c>
-      <c r="M19" s="37" t="s">
-        <v>37</v>
-      </c>
-      <c r="N19" s="41" t="s">
-        <v>275</v>
-      </c>
-      <c r="O19" s="173"/>
-      <c r="P19" s="226" t="s">
-        <v>282</v>
-      </c>
-      <c r="Q19" s="210" t="s">
-        <v>258</v>
-      </c>
-      <c r="R19" s="146"/>
-    </row>
-    <row r="20" spans="2:18">
-      <c r="B20" s="74" t="s">
-        <v>231</v>
-      </c>
-      <c r="C20" s="172" t="s">
-        <v>179</v>
-      </c>
-      <c r="D20" s="172" t="s">
-        <v>179</v>
-      </c>
-      <c r="E20" s="172" t="s">
-        <v>179</v>
-      </c>
-      <c r="F20" s="172" t="s">
-        <v>179</v>
-      </c>
-      <c r="G20" s="172" t="s">
-        <v>179</v>
-      </c>
-      <c r="H20" s="172" t="s">
-        <v>179</v>
-      </c>
-      <c r="I20" s="172" t="s">
-        <v>179</v>
-      </c>
-      <c r="J20" s="172" t="s">
-        <v>179</v>
-      </c>
-      <c r="K20" s="39" t="s">
-        <v>237</v>
-      </c>
-      <c r="L20" s="40" t="s">
-        <v>242</v>
-      </c>
-      <c r="M20" s="40" t="s">
-        <v>33</v>
-      </c>
-      <c r="N20" s="41" t="s">
-        <v>113</v>
-      </c>
-      <c r="O20" s="205"/>
-      <c r="P20" s="210" t="s">
-        <v>253</v>
-      </c>
-      <c r="Q20" s="209" t="s">
-        <v>253</v>
-      </c>
-      <c r="R20" s="145"/>
-    </row>
-    <row r="21" spans="2:18">
-      <c r="B21" s="74" t="s">
-        <v>252</v>
-      </c>
-      <c r="C21" s="173" t="s">
-        <v>179</v>
-      </c>
-      <c r="D21" s="173" t="s">
-        <v>179</v>
-      </c>
-      <c r="E21" s="173" t="s">
-        <v>179</v>
-      </c>
-      <c r="F21" s="173" t="s">
-        <v>179</v>
-      </c>
-      <c r="G21" s="173" t="s">
-        <v>179</v>
-      </c>
-      <c r="H21" s="173" t="s">
-        <v>179</v>
-      </c>
-      <c r="I21" s="173" t="s">
-        <v>179</v>
-      </c>
-      <c r="J21" s="173" t="s">
-        <v>179</v>
-      </c>
-      <c r="K21" s="197" t="s">
-        <v>237</v>
-      </c>
-      <c r="L21" s="40" t="s">
-        <v>242</v>
-      </c>
-      <c r="M21" s="37" t="s">
-        <v>35</v>
-      </c>
-      <c r="N21" s="42" t="s">
-        <v>266</v>
-      </c>
-      <c r="O21" s="173"/>
-      <c r="P21" s="210" t="s">
-        <v>253</v>
-      </c>
-      <c r="Q21" s="210" t="s">
-        <v>270</v>
-      </c>
-      <c r="R21" s="146"/>
-    </row>
-    <row r="22" spans="2:18">
-      <c r="B22" s="74" t="s">
-        <v>231</v>
-      </c>
-      <c r="C22" s="173" t="s">
-        <v>179</v>
-      </c>
-      <c r="D22" s="173" t="s">
-        <v>179</v>
-      </c>
-      <c r="E22" s="173" t="s">
-        <v>179</v>
-      </c>
-      <c r="F22" s="173" t="s">
-        <v>179</v>
-      </c>
-      <c r="G22" s="173" t="s">
-        <v>179</v>
-      </c>
-      <c r="H22" s="173" t="s">
-        <v>179</v>
-      </c>
-      <c r="I22" s="173" t="s">
-        <v>179</v>
-      </c>
-      <c r="J22" s="173" t="s">
-        <v>179</v>
-      </c>
-      <c r="K22" s="197" t="s">
-        <v>238</v>
-      </c>
-      <c r="L22" s="40" t="s">
-        <v>242</v>
-      </c>
-      <c r="M22" s="37" t="s">
-        <v>36</v>
-      </c>
-      <c r="N22" s="42" t="s">
+      <c r="K19" s="200" t="s">
+        <v>229</v>
+      </c>
+      <c r="L19" s="194" t="s">
+        <v>227</v>
+      </c>
+      <c r="M19" s="195" t="s">
         <v>34</v>
       </c>
-      <c r="O22" s="173"/>
-      <c r="P22" s="210" t="s">
-        <v>253</v>
-      </c>
-      <c r="Q22" s="210" t="s">
-        <v>253</v>
-      </c>
-      <c r="R22" s="146"/>
-    </row>
-    <row r="23" spans="2:18">
-      <c r="B23" s="74" t="s">
-        <v>231</v>
-      </c>
-      <c r="C23" s="173" t="s">
-        <v>179</v>
-      </c>
-      <c r="D23" s="173" t="s">
-        <v>179</v>
-      </c>
-      <c r="E23" s="173" t="s">
-        <v>179</v>
-      </c>
-      <c r="F23" s="173" t="s">
-        <v>179</v>
-      </c>
-      <c r="G23" s="173" t="s">
-        <v>179</v>
-      </c>
-      <c r="H23" s="173" t="s">
-        <v>179</v>
-      </c>
-      <c r="I23" s="173" t="s">
-        <v>179</v>
-      </c>
-      <c r="J23" s="173" t="s">
-        <v>179</v>
-      </c>
-      <c r="K23" s="197" t="s">
-        <v>238</v>
-      </c>
-      <c r="L23" s="40" t="s">
-        <v>242</v>
-      </c>
-      <c r="M23" s="37" t="s">
-        <v>37</v>
-      </c>
-      <c r="N23" s="42" t="s">
-        <v>34</v>
-      </c>
-      <c r="O23" s="173"/>
-      <c r="P23" s="210" t="s">
-        <v>253</v>
-      </c>
-      <c r="Q23" s="210" t="s">
-        <v>253</v>
-      </c>
-      <c r="R23" s="146"/>
-    </row>
-    <row r="24" spans="2:18">
-      <c r="B24" s="74" t="s">
-        <v>231</v>
-      </c>
-      <c r="C24" s="172" t="s">
-        <v>179</v>
-      </c>
-      <c r="D24" s="172" t="s">
-        <v>179</v>
-      </c>
-      <c r="E24" s="172" t="s">
-        <v>179</v>
-      </c>
-      <c r="F24" s="172" t="s">
-        <v>179</v>
-      </c>
-      <c r="G24" s="172" t="s">
-        <v>179</v>
-      </c>
-      <c r="H24" s="172" t="s">
-        <v>179</v>
-      </c>
-      <c r="I24" s="172" t="s">
-        <v>179</v>
-      </c>
-      <c r="J24" s="172" t="s">
-        <v>179</v>
-      </c>
-      <c r="K24" s="39" t="s">
-        <v>237</v>
-      </c>
-      <c r="L24" s="40" t="s">
-        <v>243</v>
-      </c>
-      <c r="M24" s="40" t="s">
-        <v>33</v>
-      </c>
-      <c r="N24" s="41" t="s">
-        <v>113</v>
-      </c>
-      <c r="O24" s="205"/>
-      <c r="P24" s="210" t="s">
-        <v>253</v>
-      </c>
-      <c r="Q24" s="209" t="s">
-        <v>253</v>
-      </c>
-      <c r="R24" s="145"/>
-    </row>
-    <row r="25" spans="2:18">
-      <c r="B25" s="74" t="s">
-        <v>245</v>
-      </c>
-      <c r="C25" s="173" t="s">
-        <v>179</v>
-      </c>
-      <c r="D25" s="173" t="s">
-        <v>179</v>
-      </c>
-      <c r="E25" s="173" t="s">
-        <v>179</v>
-      </c>
-      <c r="F25" s="173" t="s">
-        <v>179</v>
-      </c>
-      <c r="G25" s="173" t="s">
-        <v>179</v>
-      </c>
-      <c r="H25" s="173" t="s">
-        <v>179</v>
-      </c>
-      <c r="I25" s="173" t="s">
-        <v>179</v>
-      </c>
-      <c r="J25" s="173" t="s">
-        <v>179</v>
-      </c>
-      <c r="K25" s="197" t="s">
-        <v>237</v>
-      </c>
-      <c r="L25" s="40" t="s">
-        <v>243</v>
-      </c>
-      <c r="M25" s="37" t="s">
-        <v>35</v>
-      </c>
-      <c r="N25" s="42" t="s">
-        <v>264</v>
-      </c>
-      <c r="O25" s="173"/>
-      <c r="P25" s="210" t="s">
-        <v>253</v>
-      </c>
-      <c r="Q25" s="210" t="s">
-        <v>270</v>
-      </c>
-      <c r="R25" s="146"/>
-    </row>
-    <row r="26" spans="2:18">
-      <c r="B26" s="74" t="s">
-        <v>231</v>
-      </c>
-      <c r="C26" s="173" t="s">
-        <v>179</v>
-      </c>
-      <c r="D26" s="173" t="s">
-        <v>179</v>
-      </c>
-      <c r="E26" s="173" t="s">
-        <v>179</v>
-      </c>
-      <c r="F26" s="173" t="s">
-        <v>179</v>
-      </c>
-      <c r="G26" s="173" t="s">
-        <v>179</v>
-      </c>
-      <c r="H26" s="173" t="s">
-        <v>179</v>
-      </c>
-      <c r="I26" s="173" t="s">
-        <v>179</v>
-      </c>
-      <c r="J26" s="173" t="s">
-        <v>179</v>
-      </c>
-      <c r="K26" s="197" t="s">
-        <v>238</v>
-      </c>
-      <c r="L26" s="40" t="s">
-        <v>243</v>
-      </c>
-      <c r="M26" s="37" t="s">
-        <v>36</v>
-      </c>
-      <c r="N26" s="42" t="s">
-        <v>34</v>
-      </c>
-      <c r="O26" s="173"/>
-      <c r="P26" s="210" t="s">
-        <v>253</v>
-      </c>
-      <c r="Q26" s="210" t="s">
-        <v>253</v>
-      </c>
-      <c r="R26" s="146"/>
-    </row>
-    <row r="27" spans="2:18">
-      <c r="B27" s="74" t="s">
-        <v>231</v>
-      </c>
-      <c r="C27" s="173" t="s">
-        <v>179</v>
-      </c>
-      <c r="D27" s="173" t="s">
-        <v>179</v>
-      </c>
-      <c r="E27" s="173" t="s">
-        <v>179</v>
-      </c>
-      <c r="F27" s="173" t="s">
-        <v>179</v>
-      </c>
-      <c r="G27" s="173" t="s">
-        <v>179</v>
-      </c>
-      <c r="H27" s="173" t="s">
-        <v>179</v>
-      </c>
-      <c r="I27" s="173" t="s">
-        <v>179</v>
-      </c>
-      <c r="J27" s="173" t="s">
-        <v>179</v>
-      </c>
-      <c r="K27" s="197" t="s">
-        <v>238</v>
-      </c>
-      <c r="L27" s="40" t="s">
-        <v>243</v>
-      </c>
-      <c r="M27" s="37" t="s">
-        <v>37</v>
-      </c>
-      <c r="N27" s="42" t="s">
-        <v>34</v>
-      </c>
-      <c r="O27" s="173"/>
-      <c r="P27" s="210" t="s">
-        <v>253</v>
-      </c>
-      <c r="Q27" s="210" t="s">
-        <v>256</v>
-      </c>
-      <c r="R27" s="146"/>
-    </row>
-    <row r="28" spans="2:18">
-      <c r="B28" s="22" t="s">
-        <v>248</v>
-      </c>
-      <c r="C28" s="173" t="s">
-        <v>179</v>
-      </c>
-      <c r="D28" s="173" t="s">
-        <v>179</v>
-      </c>
-      <c r="E28" s="173" t="s">
-        <v>179</v>
-      </c>
-      <c r="F28" s="173" t="s">
-        <v>179</v>
-      </c>
-      <c r="G28" s="173" t="s">
-        <v>179</v>
-      </c>
-      <c r="H28" s="173" t="s">
-        <v>179</v>
-      </c>
-      <c r="I28" s="173" t="s">
-        <v>179</v>
-      </c>
-      <c r="J28" s="173" t="s">
-        <v>179</v>
-      </c>
-      <c r="K28" s="61" t="s">
-        <v>35</v>
-      </c>
-      <c r="L28" s="197" t="s">
-        <v>226</v>
-      </c>
-      <c r="M28" s="197" t="s">
-        <v>226</v>
-      </c>
-      <c r="N28" s="42" t="s">
-        <v>34</v>
-      </c>
-      <c r="O28" s="173"/>
-      <c r="P28" s="210" t="s">
-        <v>253</v>
-      </c>
-      <c r="Q28" s="210" t="s">
-        <v>253</v>
-      </c>
-      <c r="R28" s="146"/>
-    </row>
-    <row r="29" spans="2:18">
-      <c r="B29" s="22" t="s">
-        <v>249</v>
-      </c>
-      <c r="C29" s="173" t="s">
-        <v>179</v>
-      </c>
-      <c r="D29" s="173" t="s">
-        <v>179</v>
-      </c>
-      <c r="E29" s="173" t="s">
-        <v>179</v>
-      </c>
-      <c r="F29" s="173" t="s">
-        <v>179</v>
-      </c>
-      <c r="G29" s="173" t="s">
-        <v>179</v>
-      </c>
-      <c r="H29" s="173" t="s">
-        <v>179</v>
-      </c>
-      <c r="I29" s="173" t="s">
-        <v>179</v>
-      </c>
-      <c r="J29" s="173" t="s">
-        <v>179</v>
-      </c>
-      <c r="K29" s="61" t="s">
-        <v>36</v>
-      </c>
-      <c r="L29" s="197" t="s">
-        <v>226</v>
-      </c>
-      <c r="M29" s="197" t="s">
-        <v>226</v>
-      </c>
-      <c r="N29" s="42" t="s">
-        <v>34</v>
-      </c>
-      <c r="O29" s="173"/>
-      <c r="P29" s="210" t="s">
-        <v>253</v>
-      </c>
-      <c r="Q29" s="210" t="s">
-        <v>257</v>
-      </c>
-      <c r="R29" s="146"/>
-    </row>
-    <row r="30" spans="2:18">
-      <c r="B30" s="22" t="s">
-        <v>250</v>
-      </c>
-      <c r="C30" s="173" t="s">
-        <v>179</v>
-      </c>
-      <c r="D30" s="173" t="s">
-        <v>179</v>
-      </c>
-      <c r="E30" s="173" t="s">
-        <v>179</v>
-      </c>
-      <c r="F30" s="173" t="s">
-        <v>179</v>
-      </c>
-      <c r="G30" s="173" t="s">
-        <v>179</v>
-      </c>
-      <c r="H30" s="173" t="s">
-        <v>179</v>
-      </c>
-      <c r="I30" s="173" t="s">
-        <v>179</v>
-      </c>
-      <c r="J30" s="173" t="s">
-        <v>179</v>
-      </c>
-      <c r="K30" s="61" t="s">
-        <v>37</v>
-      </c>
-      <c r="L30" s="197" t="s">
-        <v>226</v>
-      </c>
-      <c r="M30" s="197" t="s">
-        <v>226</v>
-      </c>
-      <c r="N30" s="42" t="s">
-        <v>34</v>
-      </c>
-      <c r="O30" s="173"/>
-      <c r="P30" s="210" t="s">
-        <v>254</v>
-      </c>
-      <c r="Q30" s="210" t="s">
-        <v>253</v>
-      </c>
-      <c r="R30" s="146"/>
-    </row>
-    <row r="31" spans="2:18" ht="13.5" thickBot="1">
-      <c r="B31" s="214" t="s">
-        <v>251</v>
-      </c>
-      <c r="C31" s="215" t="s">
-        <v>179</v>
-      </c>
-      <c r="D31" s="215" t="s">
-        <v>179</v>
-      </c>
-      <c r="E31" s="215" t="s">
-        <v>179</v>
-      </c>
-      <c r="F31" s="215" t="s">
-        <v>179</v>
-      </c>
-      <c r="G31" s="215" t="s">
-        <v>179</v>
-      </c>
-      <c r="H31" s="215" t="s">
-        <v>179</v>
-      </c>
-      <c r="I31" s="215" t="s">
-        <v>179</v>
-      </c>
-      <c r="J31" s="215" t="s">
-        <v>179</v>
-      </c>
-      <c r="K31" s="201" t="s">
-        <v>233</v>
-      </c>
-      <c r="L31" s="201" t="s">
-        <v>233</v>
-      </c>
-      <c r="M31" s="194" t="s">
-        <v>227</v>
-      </c>
-      <c r="N31" s="195" t="s">
-        <v>34</v>
-      </c>
-      <c r="O31" s="193"/>
-      <c r="P31" s="211" t="s">
-        <v>255</v>
-      </c>
-      <c r="Q31" s="211" t="s">
-        <v>256</v>
-      </c>
-      <c r="R31" s="196"/>
-    </row>
-    <row r="38" spans="2:41">
-      <c r="U38" s="200" t="s">
-        <v>229</v>
-      </c>
-      <c r="V38" s="200"/>
-      <c r="W38" s="200"/>
-      <c r="X38" s="200"/>
-      <c r="Y38" s="200"/>
-      <c r="Z38" s="200"/>
-      <c r="AA38" s="200"/>
-      <c r="AB38" s="200"/>
-      <c r="AC38" s="200"/>
-      <c r="AD38" s="200"/>
-      <c r="AE38" s="200"/>
-      <c r="AF38" s="200"/>
-      <c r="AG38" s="200"/>
-      <c r="AH38" s="200"/>
-      <c r="AI38" s="200"/>
-      <c r="AJ38" s="200"/>
-      <c r="AK38" s="200"/>
-      <c r="AL38" s="200"/>
-      <c r="AM38" s="200"/>
-      <c r="AN38" s="200"/>
-      <c r="AO38" s="200"/>
-    </row>
-    <row r="40" spans="2:41">
+      <c r="N19" s="193"/>
+      <c r="O19" s="282"/>
+      <c r="P19" s="209" t="s">
+        <v>244</v>
+      </c>
+      <c r="Q19" s="196"/>
+    </row>
+    <row r="28" spans="2:17">
+      <c r="B28" s="46"/>
+      <c r="C28" s="46"/>
+      <c r="D28" s="46"/>
+      <c r="E28" s="46"/>
+      <c r="F28" s="46"/>
+      <c r="G28" s="46"/>
+      <c r="H28" s="46"/>
+      <c r="I28" s="46"/>
+      <c r="J28" s="46"/>
+      <c r="K28" s="46"/>
+      <c r="L28" s="46"/>
+      <c r="M28" s="46"/>
+      <c r="N28" s="46"/>
+      <c r="O28" s="46"/>
+      <c r="P28" s="46"/>
+      <c r="Q28" s="46"/>
+    </row>
+    <row r="29" spans="2:17">
+      <c r="B29" s="46"/>
+      <c r="C29" s="60"/>
+      <c r="D29" s="60"/>
+      <c r="E29" s="60"/>
+      <c r="F29" s="60"/>
+      <c r="G29" s="60"/>
+      <c r="H29" s="60"/>
+      <c r="I29" s="60"/>
+      <c r="J29" s="60"/>
+      <c r="K29" s="60"/>
+      <c r="L29" s="60"/>
+      <c r="M29" s="60"/>
+      <c r="N29" s="60"/>
+      <c r="O29" s="60"/>
+      <c r="P29" s="60"/>
+      <c r="Q29" s="60"/>
+    </row>
+    <row r="30" spans="2:17">
+      <c r="B30" s="46"/>
+      <c r="C30" s="60"/>
+      <c r="D30" s="60"/>
+      <c r="E30" s="60"/>
+      <c r="F30" s="60"/>
+      <c r="G30" s="60"/>
+      <c r="H30" s="60"/>
+      <c r="I30" s="60"/>
+      <c r="J30" s="60"/>
+      <c r="K30" s="60"/>
+      <c r="L30" s="60"/>
+      <c r="M30" s="60"/>
+      <c r="N30" s="60"/>
+      <c r="O30" s="60"/>
+      <c r="P30" s="60"/>
+      <c r="Q30" s="60"/>
+    </row>
+    <row r="31" spans="2:17">
+      <c r="B31" s="46"/>
+      <c r="C31" s="46"/>
+      <c r="D31" s="46"/>
+      <c r="E31" s="46"/>
+      <c r="F31" s="46"/>
+      <c r="G31" s="46"/>
+      <c r="H31" s="46"/>
+      <c r="I31" s="46"/>
+      <c r="J31" s="46"/>
+      <c r="K31" s="46"/>
+      <c r="L31" s="46"/>
+      <c r="M31" s="46"/>
+      <c r="N31" s="46"/>
+      <c r="O31" s="46"/>
+      <c r="P31" s="46"/>
+      <c r="Q31" s="46"/>
+    </row>
+    <row r="32" spans="2:17">
+      <c r="B32" s="46"/>
+      <c r="C32" s="46"/>
+      <c r="D32" s="46"/>
+      <c r="E32" s="46"/>
+      <c r="F32" s="46"/>
+      <c r="G32" s="46"/>
+      <c r="H32" s="46"/>
+      <c r="I32" s="46"/>
+      <c r="J32" s="46"/>
+      <c r="K32" s="46"/>
+      <c r="L32" s="46"/>
+      <c r="M32" s="46"/>
+      <c r="N32" s="46"/>
+      <c r="O32" s="46"/>
+      <c r="P32" s="46"/>
+      <c r="Q32" s="46"/>
+    </row>
+    <row r="38" spans="2:40">
+      <c r="T38" s="199" t="s">
+        <v>228</v>
+      </c>
+      <c r="U38" s="199"/>
+      <c r="V38" s="199"/>
+      <c r="W38" s="199"/>
+      <c r="X38" s="199"/>
+      <c r="Y38" s="199"/>
+      <c r="Z38" s="199"/>
+      <c r="AA38" s="199"/>
+      <c r="AB38" s="199"/>
+      <c r="AC38" s="199"/>
+      <c r="AD38" s="199"/>
+      <c r="AE38" s="199"/>
+      <c r="AF38" s="199"/>
+      <c r="AG38" s="199"/>
+      <c r="AH38" s="199"/>
+      <c r="AI38" s="199"/>
+      <c r="AJ38" s="199"/>
+      <c r="AK38" s="199"/>
+      <c r="AL38" s="199"/>
+      <c r="AM38" s="199"/>
+      <c r="AN38" s="199"/>
+    </row>
+    <row r="39" spans="2:40">
+      <c r="B39" s="46"/>
+      <c r="C39" s="46"/>
+      <c r="D39" s="46"/>
+      <c r="E39" s="46"/>
+      <c r="F39" s="46"/>
+      <c r="G39" s="46"/>
+      <c r="H39" s="46"/>
+      <c r="I39" s="46"/>
+      <c r="J39" s="46"/>
+      <c r="K39" s="46"/>
+      <c r="L39" s="46"/>
+      <c r="M39" s="46"/>
+      <c r="N39" s="46"/>
+      <c r="O39" s="46"/>
+      <c r="P39" s="46"/>
+      <c r="Q39" s="46"/>
+    </row>
+    <row r="40" spans="2:40">
       <c r="B40" s="46"/>
-      <c r="C40" s="46"/>
-      <c r="D40" s="46"/>
-      <c r="E40" s="46"/>
-      <c r="F40" s="46"/>
-      <c r="G40" s="46"/>
-      <c r="H40" s="46"/>
-      <c r="I40" s="46"/>
-      <c r="J40" s="46"/>
-      <c r="K40" s="46"/>
-      <c r="L40" s="46"/>
-      <c r="M40" s="46"/>
-      <c r="N40" s="46"/>
-      <c r="O40" s="46"/>
-      <c r="P40" s="46"/>
-      <c r="Q40" s="46"/>
-      <c r="R40" s="46"/>
-    </row>
-    <row r="41" spans="2:41">
+      <c r="C40" s="60"/>
+      <c r="D40" s="60"/>
+      <c r="E40" s="60"/>
+      <c r="F40" s="60"/>
+      <c r="G40" s="60"/>
+      <c r="H40" s="60"/>
+      <c r="I40" s="60"/>
+      <c r="J40" s="60"/>
+      <c r="K40" s="60"/>
+      <c r="L40" s="60"/>
+      <c r="M40" s="60"/>
+      <c r="N40" s="211"/>
+      <c r="O40" s="60"/>
+      <c r="P40" s="60"/>
+      <c r="Q40" s="60"/>
+    </row>
+    <row r="41" spans="2:40">
       <c r="B41" s="46"/>
       <c r="C41" s="60"/>
       <c r="D41" s="60"/>
@@ -45191,9 +42820,8 @@
       <c r="O41" s="60"/>
       <c r="P41" s="60"/>
       <c r="Q41" s="60"/>
-      <c r="R41" s="60"/>
-    </row>
-    <row r="42" spans="2:41">
+    </row>
+    <row r="42" spans="2:40">
       <c r="B42" s="46"/>
       <c r="C42" s="60"/>
       <c r="D42" s="60"/>
@@ -45210,28 +42838,26 @@
       <c r="O42" s="60"/>
       <c r="P42" s="60"/>
       <c r="Q42" s="60"/>
-      <c r="R42" s="60"/>
-    </row>
-    <row r="43" spans="2:41">
+    </row>
+    <row r="43" spans="2:40">
       <c r="B43" s="46"/>
-      <c r="C43" s="46"/>
-      <c r="D43" s="46"/>
-      <c r="E43" s="46"/>
-      <c r="F43" s="46"/>
-      <c r="G43" s="46"/>
-      <c r="H43" s="46"/>
-      <c r="I43" s="46"/>
-      <c r="J43" s="46"/>
-      <c r="K43" s="46"/>
-      <c r="L43" s="46"/>
-      <c r="M43" s="46"/>
-      <c r="N43" s="46"/>
-      <c r="O43" s="46"/>
-      <c r="P43" s="46"/>
-      <c r="Q43" s="46"/>
-      <c r="R43" s="46"/>
-    </row>
-    <row r="44" spans="2:41">
+      <c r="C43" s="60"/>
+      <c r="D43" s="60"/>
+      <c r="E43" s="60"/>
+      <c r="F43" s="60"/>
+      <c r="G43" s="60"/>
+      <c r="H43" s="60"/>
+      <c r="I43" s="60"/>
+      <c r="J43" s="60"/>
+      <c r="K43" s="60"/>
+      <c r="L43" s="60"/>
+      <c r="M43" s="60"/>
+      <c r="N43" s="60"/>
+      <c r="O43" s="60"/>
+      <c r="P43" s="60"/>
+      <c r="Q43" s="60"/>
+    </row>
+    <row r="44" spans="2:40">
       <c r="B44" s="46"/>
       <c r="C44" s="46"/>
       <c r="D44" s="46"/>
@@ -45248,190 +42874,24 @@
       <c r="O44" s="46"/>
       <c r="P44" s="46"/>
       <c r="Q44" s="46"/>
-      <c r="R44" s="46"/>
-    </row>
-    <row r="51" spans="2:18">
-      <c r="B51" s="46"/>
-      <c r="C51" s="46"/>
-      <c r="D51" s="46"/>
-      <c r="E51" s="46"/>
-      <c r="F51" s="46"/>
-      <c r="G51" s="46"/>
-      <c r="H51" s="46"/>
-      <c r="I51" s="46"/>
-      <c r="J51" s="46"/>
-      <c r="K51" s="46"/>
-      <c r="L51" s="46"/>
-      <c r="M51" s="46"/>
-      <c r="N51" s="46"/>
-      <c r="O51" s="46"/>
-      <c r="P51" s="46"/>
-      <c r="Q51" s="46"/>
-      <c r="R51" s="46"/>
-    </row>
-    <row r="52" spans="2:18">
-      <c r="B52" s="46"/>
-      <c r="C52" s="60"/>
-      <c r="D52" s="60"/>
-      <c r="E52" s="60"/>
-      <c r="F52" s="60"/>
-      <c r="G52" s="60"/>
-      <c r="H52" s="60"/>
-      <c r="I52" s="60"/>
-      <c r="J52" s="60"/>
-      <c r="K52" s="60"/>
-      <c r="L52" s="60"/>
-      <c r="M52" s="60"/>
-      <c r="N52" s="60"/>
-      <c r="O52" s="213"/>
-      <c r="P52" s="60"/>
-      <c r="Q52" s="60"/>
-      <c r="R52" s="60"/>
-    </row>
-    <row r="53" spans="2:18">
-      <c r="B53" s="46"/>
-      <c r="C53" s="60"/>
-      <c r="D53" s="60"/>
-      <c r="E53" s="60"/>
-      <c r="F53" s="60"/>
-      <c r="G53" s="60"/>
-      <c r="H53" s="60"/>
-      <c r="I53" s="60"/>
-      <c r="J53" s="60"/>
-      <c r="K53" s="60"/>
-      <c r="L53" s="60"/>
-      <c r="M53" s="60"/>
-      <c r="N53" s="60"/>
-      <c r="O53" s="60"/>
-      <c r="P53" s="60"/>
-      <c r="Q53" s="60"/>
-      <c r="R53" s="60"/>
-    </row>
-    <row r="54" spans="2:18">
-      <c r="B54" s="46"/>
-      <c r="C54" s="60"/>
-      <c r="D54" s="60"/>
-      <c r="E54" s="60"/>
-      <c r="F54" s="60"/>
-      <c r="G54" s="60"/>
-      <c r="H54" s="60"/>
-      <c r="I54" s="60"/>
-      <c r="J54" s="60"/>
-      <c r="K54" s="60"/>
-      <c r="L54" s="60"/>
-      <c r="M54" s="60"/>
-      <c r="N54" s="60"/>
-      <c r="O54" s="60"/>
-      <c r="P54" s="60"/>
-      <c r="Q54" s="60"/>
-      <c r="R54" s="60"/>
-    </row>
-    <row r="55" spans="2:18">
-      <c r="B55" s="46"/>
-      <c r="C55" s="60"/>
-      <c r="D55" s="60"/>
-      <c r="E55" s="60"/>
-      <c r="F55" s="60"/>
-      <c r="G55" s="60"/>
-      <c r="H55" s="60"/>
-      <c r="I55" s="60"/>
-      <c r="J55" s="60"/>
-      <c r="K55" s="60"/>
-      <c r="L55" s="60"/>
-      <c r="M55" s="60"/>
-      <c r="N55" s="60"/>
-      <c r="O55" s="60"/>
-      <c r="P55" s="60"/>
-      <c r="Q55" s="60"/>
-      <c r="R55" s="60"/>
-    </row>
-    <row r="56" spans="2:18">
-      <c r="B56" s="46"/>
-      <c r="C56" s="46"/>
-      <c r="D56" s="46"/>
-      <c r="E56" s="46"/>
-      <c r="F56" s="46"/>
-      <c r="G56" s="46"/>
-      <c r="H56" s="46"/>
-      <c r="I56" s="46"/>
-      <c r="J56" s="46"/>
-      <c r="K56" s="46"/>
-      <c r="L56" s="46"/>
-      <c r="M56" s="46"/>
-      <c r="N56" s="46"/>
-      <c r="O56" s="46"/>
-      <c r="P56" s="46"/>
-      <c r="Q56" s="46"/>
-      <c r="R56" s="46"/>
-    </row>
-    <row r="57" spans="2:18">
-      <c r="B57" s="46"/>
-      <c r="C57" s="46"/>
-      <c r="D57" s="46"/>
-      <c r="E57" s="46"/>
-      <c r="F57" s="46"/>
-      <c r="G57" s="46"/>
-      <c r="H57" s="46"/>
-      <c r="I57" s="46"/>
-      <c r="J57" s="46"/>
-      <c r="K57" s="46"/>
-      <c r="L57" s="46"/>
-      <c r="M57" s="46"/>
-      <c r="N57" s="46"/>
-      <c r="O57" s="46"/>
-      <c r="P57" s="46"/>
-      <c r="Q57" s="46"/>
-      <c r="R57" s="46"/>
-    </row>
-    <row r="80" spans="21:41">
-      <c r="U80" s="200" t="s">
-        <v>230</v>
-      </c>
-      <c r="V80" s="200"/>
-      <c r="W80" s="200"/>
-      <c r="X80" s="200"/>
-      <c r="Y80" s="200"/>
-      <c r="Z80" s="200"/>
-      <c r="AA80" s="200"/>
-      <c r="AB80" s="200"/>
-      <c r="AC80" s="200"/>
-      <c r="AD80" s="200"/>
-      <c r="AE80" s="200"/>
-      <c r="AF80" s="200"/>
-      <c r="AG80" s="200"/>
-      <c r="AH80" s="200"/>
-      <c r="AI80" s="200"/>
-      <c r="AJ80" s="200"/>
-      <c r="AK80" s="200"/>
-      <c r="AL80" s="200"/>
-      <c r="AM80" s="200"/>
-      <c r="AN80" s="200"/>
-      <c r="AO80" s="200"/>
-    </row>
-    <row r="120" spans="21:41">
-      <c r="U120" s="200" t="s">
-        <v>288</v>
-      </c>
-      <c r="V120" s="200"/>
-      <c r="W120" s="200"/>
-      <c r="X120" s="200"/>
-      <c r="Y120" s="200"/>
-      <c r="Z120" s="200"/>
-      <c r="AA120" s="200"/>
-      <c r="AB120" s="200"/>
-      <c r="AC120" s="200"/>
-      <c r="AD120" s="200"/>
-      <c r="AE120" s="200"/>
-      <c r="AF120" s="200"/>
-      <c r="AG120" s="200"/>
-      <c r="AH120" s="200"/>
-      <c r="AI120" s="200"/>
-      <c r="AJ120" s="200"/>
-      <c r="AK120" s="200"/>
-      <c r="AL120" s="200"/>
-      <c r="AM120" s="200"/>
-      <c r="AN120" s="200"/>
-      <c r="AO120" s="200"/>
+    </row>
+    <row r="45" spans="2:40">
+      <c r="B45" s="46"/>
+      <c r="C45" s="46"/>
+      <c r="D45" s="46"/>
+      <c r="E45" s="46"/>
+      <c r="F45" s="46"/>
+      <c r="G45" s="46"/>
+      <c r="H45" s="46"/>
+      <c r="I45" s="46"/>
+      <c r="J45" s="46"/>
+      <c r="K45" s="46"/>
+      <c r="L45" s="46"/>
+      <c r="M45" s="46"/>
+      <c r="N45" s="46"/>
+      <c r="O45" s="46"/>
+      <c r="P45" s="46"/>
+      <c r="Q45" s="46"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -45458,14 +42918,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <sheetPr codeName="Sheet6"/>
   <dimension ref="B2:D27"/>
-  <sheetFormatPr defaultRowHeight="13"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="2" max="2" width="4.90625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.26953125" customWidth="1"/>
+    <col min="2" max="2" width="4.875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.25" customWidth="1"/>
     <col min="4" max="4" width="86" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:4" ht="13.5" thickBot="1">
+    <row r="2" spans="2:4" ht="14.25" thickBot="1">
       <c r="B2" s="83" t="s">
         <v>90</v>
       </c>
@@ -45475,7 +42935,7 @@
       </c>
       <c r="D2" s="84"/>
     </row>
-    <row r="3" spans="2:4" ht="13.5" thickBot="1">
+    <row r="3" spans="2:4" ht="14.25" thickBot="1">
       <c r="B3" s="77" t="s">
         <v>90</v>
       </c>
@@ -45486,7 +42946,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="4" spans="2:4" ht="13.5" thickTop="1">
+    <row r="4" spans="2:4" ht="14.25" thickTop="1">
       <c r="B4" s="12">
         <v>0</v>
       </c>
@@ -45497,7 +42957,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="2:4" ht="39">
+    <row r="5" spans="2:4" ht="40.5">
       <c r="B5" s="2">
         <v>1</v>
       </c>
@@ -45508,7 +42968,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="6" spans="2:4" ht="26">
+    <row r="6" spans="2:4" ht="27">
       <c r="B6" s="2">
         <v>2</v>
       </c>
@@ -45519,7 +42979,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="7" spans="2:4" ht="52">
+    <row r="7" spans="2:4" ht="54">
       <c r="B7" s="2">
         <v>3</v>
       </c>
@@ -45530,7 +42990,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="8" spans="2:4" ht="78">
+    <row r="8" spans="2:4" ht="81">
       <c r="B8" s="2">
         <v>4</v>
       </c>
@@ -45552,7 +43012,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="10" spans="2:4" ht="26">
+    <row r="10" spans="2:4" ht="27">
       <c r="B10" s="2">
         <v>6</v>
       </c>
@@ -45563,7 +43023,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="11" spans="2:4" ht="26">
+    <row r="11" spans="2:4" ht="27">
       <c r="B11" s="2">
         <v>7</v>
       </c>
@@ -45574,7 +43034,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="12" spans="2:4" ht="26">
+    <row r="12" spans="2:4" ht="27">
       <c r="B12" s="2">
         <v>8</v>
       </c>
@@ -45585,7 +43045,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="13" spans="2:4" ht="26">
+    <row r="13" spans="2:4" ht="27">
       <c r="B13" s="2">
         <v>9</v>
       </c>
@@ -45596,7 +43056,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="14" spans="2:4" ht="26">
+    <row r="14" spans="2:4" ht="27">
       <c r="B14" s="2">
         <v>10</v>
       </c>
@@ -45607,7 +43067,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="15" spans="2:4" ht="130">
+    <row r="15" spans="2:4" ht="135">
       <c r="B15" s="2">
         <v>11</v>
       </c>
@@ -45629,7 +43089,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="17" spans="2:4" ht="26">
+    <row r="17" spans="2:4" ht="27">
       <c r="B17" s="2">
         <v>13</v>
       </c>
@@ -45640,7 +43100,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="18" spans="2:4" ht="91">
+    <row r="18" spans="2:4" ht="67.5">
       <c r="B18" s="2">
         <v>14</v>
       </c>
@@ -45651,7 +43111,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="19" spans="2:4" ht="39">
+    <row r="19" spans="2:4" ht="40.5">
       <c r="B19" s="2">
         <v>15</v>
       </c>
@@ -45684,26 +43144,26 @@
         <v>214</v>
       </c>
     </row>
-    <row r="22" spans="2:4" ht="26">
+    <row r="22" spans="2:4" ht="27">
       <c r="B22" s="2">
         <v>18</v>
       </c>
       <c r="C22" s="87" t="s">
-        <v>276</v>
+        <v>254</v>
       </c>
       <c r="D22" s="89" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="23" spans="2:4" ht="26">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="23" spans="2:4" ht="27">
       <c r="B23" s="2">
         <v>19</v>
       </c>
       <c r="C23" s="87" t="s">
-        <v>276</v>
+        <v>254</v>
       </c>
       <c r="D23" s="89" t="s">
-        <v>278</v>
+        <v>256</v>
       </c>
     </row>
     <row r="24" spans="2:4">
@@ -45721,7 +43181,7 @@
       <c r="C26" s="87"/>
       <c r="D26" s="76"/>
     </row>
-    <row r="27" spans="2:4" ht="13.5" thickBot="1">
+    <row r="27" spans="2:4" ht="14.25" thickBot="1">
       <c r="B27" s="3"/>
       <c r="C27" s="88"/>
       <c r="D27" s="5"/>
